--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,22 +8436,22 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16415,10 +16415,10 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21143,10 +21143,10 @@
         <v>0</v>
       </c>
       <c r="AG105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16415,10 +16415,10 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16809,10 +16809,10 @@
         <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,22 +8042,22 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,22 +11391,22 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20355,10 +20355,10 @@
         <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21143,10 +21143,10 @@
         <v>0</v>
       </c>
       <c r="AG105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,22 +26166,22 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,7 +3708,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -3718,12 +3718,12 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16809,10 +16809,10 @@
         <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20355,10 +20355,10 @@
         <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,7 +24984,7 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25816,7 +25816,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,22 +8633,22 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10450,7 +10450,7 @@
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20355,10 +20355,10 @@
         <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23649,7 +23649,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25816,7 +25816,7 @@
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q133" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R133" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q134" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R134" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH79" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,22 +17892,22 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.58</v>
+        <v>3.36</v>
       </c>
       <c r="R99" t="n">
-        <v>10.4</v>
+        <v>3.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20355,10 +20355,10 @@
         <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21143,10 +21143,10 @@
         <v>0</v>
       </c>
       <c r="AG105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23649,7 +23649,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3905,7 +3905,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16021,10 +16021,10 @@
         <v>0</v>
       </c>
       <c r="AG79" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH79" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI79" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16415,10 +16415,10 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH81" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.36</v>
+        <v>5.58</v>
       </c>
       <c r="R99" t="n">
-        <v>3.4</v>
+        <v>10.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20552,10 +20552,10 @@
         <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH102" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21143,10 +21143,10 @@
         <v>0</v>
       </c>
       <c r="AG105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,7 +22029,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,22 +25969,22 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26560,22 +26560,22 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26608,13 +26608,13 @@
         </is>
       </c>
       <c r="P133" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q133" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R133" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="S133" t="n">
         <v>0</v>
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,13 +26805,13 @@
         </is>
       </c>
       <c r="P134" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q134" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R134" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S134" t="n">
         <v>0</v>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20355,10 +20355,10 @@
         <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20552,10 +20552,10 @@
         <v>0</v>
       </c>
       <c r="AG102" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH102" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21679,7 +21679,7 @@
       </c>
       <c r="O108" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,22 +22423,22 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3905,22 +3905,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -4112,12 +4112,12 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,22 +6269,22 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10844,7 +10844,7 @@
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,22 +11785,22 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16415,10 +16415,10 @@
         <v>0</v>
       </c>
       <c r="AG81" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH81" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,22 +18089,22 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF91" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="R92" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q94" t="n">
-        <v>5.58</v>
+        <v>3.36</v>
       </c>
       <c r="R94" t="n">
-        <v>10.4</v>
+        <v>3.4</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20355,10 +20355,10 @@
         <v>0</v>
       </c>
       <c r="AG101" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH101" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21876,7 +21876,7 @@
       </c>
       <c r="O109" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,22 +22817,22 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,7 +25181,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26013,7 +26013,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2920,22 +2920,22 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3117,22 +3117,22 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,22 +7845,22 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10253,7 +10253,7 @@
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16809,10 +16809,10 @@
         <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,22 +18286,22 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18379,10 +18379,10 @@
         <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG91" t="n">
         <v>0</v>
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R99" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21143,10 +21143,10 @@
         <v>0</v>
       </c>
       <c r="AG105" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH105" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Borac Banja Luka</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnik Bijeljina</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Sloga Doboj</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Posusje</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26013,7 +26013,7 @@
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G131" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI134"/>
+  <dimension ref="A1:BI135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2127,12 +2127,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>08:30</t>
+          <t>08:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>NorthEast United</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Odisha FC</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2315,7 +2315,7 @@
         <v>0</v>
       </c>
       <c r="BI9" s="3" t="n">
-        <v>46101.35416666666</v>
+        <v>46101.33333333334</v>
       </c>
     </row>
     <row r="10">
@@ -2324,27 +2324,27 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>08:35</t>
+          <t>08:30</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Qingdao Jonoon</t>
+          <t>NorthEast United</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Zhejiang FC</t>
+          <t>Odisha FC</t>
         </is>
       </c>
       <c r="G10" t="n">
@@ -2512,7 +2512,7 @@
         <v>0</v>
       </c>
       <c r="BI10" s="3" t="n">
-        <v>46101.35763888889</v>
+        <v>46101.35416666666</v>
       </c>
     </row>
     <row r="11">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>09:00</t>
+          <t>08:35</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2536,12 +2536,12 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Qingdao Jonoon</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Zhejiang FC</t>
         </is>
       </c>
       <c r="G11" t="n">
@@ -2709,7 +2709,7 @@
         <v>0</v>
       </c>
       <c r="BI11" s="3" t="n">
-        <v>46101.375</v>
+        <v>46101.35763888889</v>
       </c>
     </row>
     <row r="12">
@@ -2718,12 +2718,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>10:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Ordabasy</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kaisar</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2906,7 +2906,7 @@
         <v>0</v>
       </c>
       <c r="BI12" s="3" t="n">
-        <v>46101.41666666666</v>
+        <v>46101.375</v>
       </c>
     </row>
     <row r="13">
@@ -2915,12 +2915,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3103,7 +3103,7 @@
         <v>0</v>
       </c>
       <c r="BI13" s="3" t="n">
-        <v>46101.45833333334</v>
+        <v>46101.375</v>
       </c>
     </row>
     <row r="14">
@@ -3112,27 +3112,27 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:00</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Ordabasy</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Kaisar</t>
         </is>
       </c>
       <c r="G14" t="n">
@@ -3300,7 +3300,7 @@
         <v>0</v>
       </c>
       <c r="BI14" s="3" t="n">
-        <v>46101.45833333334</v>
+        <v>46101.41666666666</v>
       </c>
     </row>
     <row r="15">
@@ -3309,27 +3309,27 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Sogdiana</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G15" t="n">
@@ -3497,7 +3497,7 @@
         <v>0</v>
       </c>
       <c r="BI15" s="3" t="n">
-        <v>46101.51041666666</v>
+        <v>46101.42708333334</v>
       </c>
     </row>
     <row r="16">
@@ -3506,27 +3506,27 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46101.54166666666</v>
+        <v>46101.45833333334</v>
       </c>
     </row>
     <row r="17">
@@ -3703,27 +3703,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46101.54166666666</v>
+        <v>46101.45833333334</v>
       </c>
     </row>
     <row r="18">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46101.54166666666</v>
+        <v>46101.51041666666</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46101.5625</v>
+        <v>46101.54166666666</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46101.5625</v>
+        <v>46101.54166666666</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46101.58333333334</v>
+        <v>46101.54166666666</v>
       </c>
     </row>
     <row r="22">
@@ -4688,27 +4688,27 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46101.58333333334</v>
+        <v>46101.5625</v>
       </c>
     </row>
     <row r="23">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46101.58333333334</v>
+        <v>46101.5625</v>
       </c>
     </row>
     <row r="24">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5284,22 +5284,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,22 +8239,22 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8825,27 +8825,27 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9013,7 +9013,7 @@
         <v>0</v>
       </c>
       <c r="BI43" s="3" t="n">
-        <v>46101.60416666666</v>
+        <v>46101.58333333334</v>
       </c>
     </row>
     <row r="44">
@@ -9022,12 +9022,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9210,7 +9210,7 @@
         <v>0</v>
       </c>
       <c r="BI44" s="3" t="n">
-        <v>46101.60416666666</v>
+        <v>46101.58333333334</v>
       </c>
     </row>
     <row r="45">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9407,7 +9407,7 @@
         <v>0</v>
       </c>
       <c r="BI45" s="3" t="n">
-        <v>46101.60416666666</v>
+        <v>46101.58333333334</v>
       </c>
     </row>
     <row r="46">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46101.625</v>
+        <v>46101.60416666666</v>
       </c>
     </row>
     <row r="48">
@@ -9810,12 +9810,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46101.625</v>
+        <v>46101.60416666666</v>
       </c>
     </row>
     <row r="49">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46101.625</v>
+        <v>46101.60416666666</v>
       </c>
     </row>
     <row r="50">
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46101.64583333334</v>
+        <v>46101.625</v>
       </c>
     </row>
     <row r="51">
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46101.64583333334</v>
+        <v>46101.625</v>
       </c>
     </row>
     <row r="52">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46101.64583333334</v>
+        <v>46101.625</v>
       </c>
     </row>
     <row r="53">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,22 +10997,22 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P54" t="n">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12174,12 +12174,12 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12362,7 +12362,7 @@
         <v>0</v>
       </c>
       <c r="BI60" s="3" t="n">
-        <v>46101.66666666666</v>
+        <v>46101.64583333334</v>
       </c>
     </row>
     <row r="61">
@@ -12371,12 +12371,12 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12559,7 +12559,7 @@
         <v>0</v>
       </c>
       <c r="BI61" s="3" t="n">
-        <v>46101.66666666666</v>
+        <v>46101.64583333334</v>
       </c>
     </row>
     <row r="62">
@@ -12568,12 +12568,12 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12756,7 +12756,7 @@
         <v>0</v>
       </c>
       <c r="BI62" s="3" t="n">
-        <v>46101.66666666666</v>
+        <v>46101.64583333334</v>
       </c>
     </row>
     <row r="63">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15720,12 +15720,12 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15908,7 +15908,7 @@
         <v>0</v>
       </c>
       <c r="BI78" s="3" t="n">
-        <v>46101.67708333334</v>
+        <v>46101.66666666666</v>
       </c>
     </row>
     <row r="79">
@@ -15917,12 +15917,12 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16105,7 +16105,7 @@
         <v>0</v>
       </c>
       <c r="BI79" s="3" t="n">
-        <v>46101.6875</v>
+        <v>46101.66666666666</v>
       </c>
     </row>
     <row r="80">
@@ -16114,12 +16114,12 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16302,7 +16302,7 @@
         <v>0</v>
       </c>
       <c r="BI80" s="3" t="n">
-        <v>46101.6875</v>
+        <v>46101.66666666666</v>
       </c>
     </row>
     <row r="81">
@@ -16311,12 +16311,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46101.6875</v>
+        <v>46101.67708333334</v>
       </c>
     </row>
     <row r="82">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16809,10 +16809,10 @@
         <v>0</v>
       </c>
       <c r="AG83" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH83" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17597,10 +17597,10 @@
         <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH87" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17887,27 +17887,27 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18075,7 +18075,7 @@
         <v>0</v>
       </c>
       <c r="BI89" s="3" t="n">
-        <v>46101.69791666666</v>
+        <v>46101.6875</v>
       </c>
     </row>
     <row r="90">
@@ -18084,12 +18084,12 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18272,7 +18272,7 @@
         <v>0</v>
       </c>
       <c r="BI90" s="3" t="n">
-        <v>46101.69791666666</v>
+        <v>46101.6875</v>
       </c>
     </row>
     <row r="91">
@@ -18281,12 +18281,12 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18469,7 +18469,7 @@
         <v>0</v>
       </c>
       <c r="BI91" s="3" t="n">
-        <v>46101.69791666666</v>
+        <v>46101.6875</v>
       </c>
     </row>
     <row r="92">
@@ -18483,22 +18483,22 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,22 +18680,22 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.77</v>
+        <v>3.36</v>
       </c>
       <c r="R99" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R100" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20251,7 +20251,7 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20439,7 +20439,7 @@
         <v>0</v>
       </c>
       <c r="BI101" s="3" t="n">
-        <v>46101.70833333334</v>
+        <v>46101.69791666666</v>
       </c>
     </row>
     <row r="102">
@@ -20448,12 +20448,12 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20636,7 +20636,7 @@
         <v>0</v>
       </c>
       <c r="BI102" s="3" t="n">
-        <v>46101.70833333334</v>
+        <v>46101.69791666666</v>
       </c>
     </row>
     <row r="103">
@@ -20645,12 +20645,12 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20833,7 +20833,7 @@
         <v>0</v>
       </c>
       <c r="BI103" s="3" t="n">
-        <v>46101.70833333334</v>
+        <v>46101.69791666666</v>
       </c>
     </row>
     <row r="104">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH104" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21143,10 +21143,10 @@
         <v>0</v>
       </c>
       <c r="AG105" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI105" t="n">
         <v>0</v>
@@ -21236,12 +21236,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46101.71875</v>
+        <v>46101.70833333334</v>
       </c>
     </row>
     <row r="107">
@@ -21433,12 +21433,12 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21621,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
-        <v>46101.85416666666</v>
+        <v>46101.70833333334</v>
       </c>
     </row>
     <row r="108">
@@ -21630,27 +21630,27 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="BI108" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.70833333334</v>
       </c>
     </row>
     <row r="109">
@@ -21827,12 +21827,12 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22015,7 +22015,7 @@
         <v>0</v>
       </c>
       <c r="BI109" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.71875</v>
       </c>
     </row>
     <row r="110">
@@ -22024,27 +22024,27 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Borac Banja Luka</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Radnik Bijeljina</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22212,7 +22212,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.85416666666</v>
       </c>
     </row>
     <row r="111">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Sloga Doboj</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Posusje</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22620,7 +22620,7 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -22630,12 +22630,12 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25378,7 +25378,7 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26358,27 +26358,27 @@
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26546,7 +26546,7 @@
         <v>0</v>
       </c>
       <c r="BI132" s="3" t="n">
-        <v>46101.89583333334</v>
+        <v>46101.875</v>
       </c>
     </row>
     <row r="133">
@@ -26555,12 +26555,12 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26743,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="BI133" s="3" t="n">
-        <v>46101.95833333334</v>
+        <v>46101.89583333334</v>
       </c>
     </row>
     <row r="134">
@@ -26757,22 +26757,22 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26805,141 +26805,338 @@
         </is>
       </c>
       <c r="P134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI134" s="3" t="n">
+        <v>46101.95833333334</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="G135" t="n">
+        <v>0</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0</v>
+      </c>
+      <c r="M135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N135" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O135" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P135" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q134" t="n">
+      <c r="Q135" t="n">
         <v>4.4</v>
       </c>
-      <c r="R134" t="n">
+      <c r="R135" t="n">
         <v>5.38</v>
       </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI134" s="3" t="n">
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI135" s="3" t="n">
         <v>46101.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI135"/>
+  <dimension ref="A1:BI137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,22 +2132,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46101.51041666666</v>
+        <v>46101.5</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46101.54166666666</v>
+        <v>46101.51041666666</v>
       </c>
     </row>
     <row r="20">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4688,12 +4688,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4876,7 +4876,7 @@
         <v>0</v>
       </c>
       <c r="BI22" s="3" t="n">
-        <v>46101.5625</v>
+        <v>46101.54166666666</v>
       </c>
     </row>
     <row r="23">
@@ -5082,12 +5082,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46101.58333333334</v>
+        <v>46101.5625</v>
       </c>
     </row>
     <row r="25">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9416,12 +9416,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9604,7 +9604,7 @@
         <v>0</v>
       </c>
       <c r="BI46" s="3" t="n">
-        <v>46101.60416666666</v>
+        <v>46101.58333333334</v>
       </c>
     </row>
     <row r="47">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -10204,12 +10204,12 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.99</v>
+        <v>5.88</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="R50" t="n">
-        <v>2.18</v>
+        <v>1.73</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10392,7 +10392,7 @@
         <v>0</v>
       </c>
       <c r="BI50" s="3" t="n">
-        <v>46101.625</v>
+        <v>46101.60416666666</v>
       </c>
     </row>
     <row r="51">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46101.64583333334</v>
+        <v>46101.625</v>
       </c>
     </row>
     <row r="54">
@@ -10992,27 +10992,27 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11180,7 +11180,7 @@
         <v>0</v>
       </c>
       <c r="BI54" s="3" t="n">
-        <v>46101.64583333334</v>
+        <v>46101.625</v>
       </c>
     </row>
     <row r="55">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,7 +11435,7 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12765,12 +12765,12 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,7 +12814,7 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P63" t="n">
@@ -12953,7 +12953,7 @@
         <v>0</v>
       </c>
       <c r="BI63" s="3" t="n">
-        <v>46101.66666666666</v>
+        <v>46101.64583333334</v>
       </c>
     </row>
     <row r="64">
@@ -12962,12 +12962,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13150,7 +13150,7 @@
         <v>0</v>
       </c>
       <c r="BI64" s="3" t="n">
-        <v>46101.66666666666</v>
+        <v>46101.64583333334</v>
       </c>
     </row>
     <row r="65">
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16311,12 +16311,12 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16499,7 +16499,7 @@
         <v>0</v>
       </c>
       <c r="BI81" s="3" t="n">
-        <v>46101.67708333334</v>
+        <v>46101.66666666666</v>
       </c>
     </row>
     <row r="82">
@@ -16508,12 +16508,12 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16696,7 +16696,7 @@
         <v>0</v>
       </c>
       <c r="BI82" s="3" t="n">
-        <v>46101.6875</v>
+        <v>46101.66666666666</v>
       </c>
     </row>
     <row r="83">
@@ -16705,12 +16705,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46101.6875</v>
+        <v>46101.67708333334</v>
       </c>
     </row>
     <row r="84">
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18478,27 +18478,27 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.49</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18666,7 +18666,7 @@
         <v>0</v>
       </c>
       <c r="BI92" s="3" t="n">
-        <v>46101.69791666666</v>
+        <v>46101.6875</v>
       </c>
     </row>
     <row r="93">
@@ -18675,27 +18675,27 @@
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18863,7 +18863,7 @@
         <v>0</v>
       </c>
       <c r="BI93" s="3" t="n">
-        <v>46101.69791666666</v>
+        <v>46101.6875</v>
       </c>
     </row>
     <row r="94">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.35</v>
+        <v>2.36</v>
       </c>
       <c r="Q97" t="n">
-        <v>5.58</v>
+        <v>3.36</v>
       </c>
       <c r="R97" t="n">
-        <v>10.4</v>
+        <v>3.4</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.36</v>
+        <v>3.49</v>
       </c>
       <c r="R99" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R102" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20842,12 +20842,12 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20946,10 +20946,10 @@
         <v>0</v>
       </c>
       <c r="AG104" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH104" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI104" t="n">
         <v>0</v>
@@ -21030,7 +21030,7 @@
         <v>0</v>
       </c>
       <c r="BI104" s="3" t="n">
-        <v>46101.70833333334</v>
+        <v>46101.69791666666</v>
       </c>
     </row>
     <row r="105">
@@ -21039,27 +21039,27 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21227,7 +21227,7 @@
         <v>0</v>
       </c>
       <c r="BI105" s="3" t="n">
-        <v>46101.70833333334</v>
+        <v>46101.69791666666</v>
       </c>
     </row>
     <row r="106">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21537,10 +21537,10 @@
         <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21827,27 +21827,27 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22015,7 +22015,7 @@
         <v>0</v>
       </c>
       <c r="BI109" s="3" t="n">
-        <v>46101.71875</v>
+        <v>46101.70833333334</v>
       </c>
     </row>
     <row r="110">
@@ -22024,12 +22024,12 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22212,7 +22212,7 @@
         <v>0</v>
       </c>
       <c r="BI110" s="3" t="n">
-        <v>46101.85416666666</v>
+        <v>46101.70833333334</v>
       </c>
     </row>
     <row r="111">
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.71875</v>
       </c>
     </row>
     <row r="112">
@@ -22418,27 +22418,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.85416666666</v>
       </c>
     </row>
     <row r="113">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Sarajevo</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Velež</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,7 +24196,7 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24984,22 +24984,22 @@
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25969,7 +25969,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -25979,12 +25979,12 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Sarajevo</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Velež</t>
         </is>
       </c>
       <c r="G130" t="n">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26555,27 +26555,27 @@
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26743,7 +26743,7 @@
         <v>0</v>
       </c>
       <c r="BI133" s="3" t="n">
-        <v>46101.89583333334</v>
+        <v>46101.875</v>
       </c>
     </row>
     <row r="134">
@@ -26752,27 +26752,27 @@
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26940,7 +26940,7 @@
         <v>0</v>
       </c>
       <c r="BI134" s="3" t="n">
-        <v>46101.95833333334</v>
+        <v>46101.875</v>
       </c>
     </row>
     <row r="135">
@@ -26949,27 +26949,27 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G135" t="n">
@@ -27002,141 +27002,535 @@
         </is>
       </c>
       <c r="P135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI135" s="3" t="n">
+        <v>46101.89583333334</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="G136" t="n">
+        <v>0</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0</v>
+      </c>
+      <c r="M136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N136" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O136" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI136" s="3" t="n">
+        <v>46101.95833333334</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="G137" t="n">
+        <v>0</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0</v>
+      </c>
+      <c r="M137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N137" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O137" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P137" t="n">
         <v>1.6</v>
       </c>
-      <c r="Q135" t="n">
+      <c r="Q137" t="n">
         <v>4.4</v>
       </c>
-      <c r="R135" t="n">
+      <c r="R137" t="n">
         <v>5.38</v>
       </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI135" s="3" t="n">
+      <c r="S137" t="n">
+        <v>0</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI137" s="3" t="n">
         <v>46101.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1935,22 +1935,22 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,22 +4496,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="Q29" t="n">
-        <v>5.32</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>8.369999999999999</v>
+        <v>4.09</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6756,10 +6756,10 @@
         <v>0</v>
       </c>
       <c r="AE32" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF32" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -11194,22 +11194,22 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q70" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R70" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17597,10 +17597,10 @@
         <v>0</v>
       </c>
       <c r="AG87" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17794,10 +17794,10 @@
         <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH88" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18877,22 +18877,22 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.36</v>
+        <v>3.49</v>
       </c>
       <c r="R97" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.49</v>
+        <v>3.36</v>
       </c>
       <c r="R99" t="n">
-        <v>2.81</v>
+        <v>3.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q102" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R102" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21537,10 +21537,10 @@
         <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21734,10 +21734,10 @@
         <v>0</v>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Bačka Topola</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Radnički Kragujevac</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Zrinjski</t>
+          <t>Red Star Belgrade</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Rudar Prijedor</t>
+          <t>Radnički Niš</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Čukarički</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Železničar Pančevo</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>OFK Beograd</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>IMT Novi Beograd</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>LFK Mladost Lučani</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Partizan</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Vojvodina</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Napredak</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,7 +24590,7 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25575,7 +25575,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -25585,12 +25585,12 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zrinjski</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Rudar Prijedor</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25619,7 +25619,7 @@
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -25772,7 +25772,7 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -25782,12 +25782,12 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Javor Ivanjica</t>
+          <t>Široki Brijeg</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Novi Pazar</t>
+          <t>Željezničar</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -26166,7 +26166,7 @@
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -26176,12 +26176,12 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G131" t="n">
@@ -26363,7 +26363,7 @@
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -26373,12 +26373,12 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G132" t="n">
@@ -26560,7 +26560,7 @@
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -26570,12 +26570,12 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Široki Brijeg</t>
+          <t>Javor Ivanjica</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Željezničar</t>
+          <t>Novi Pazar</t>
         </is>
       </c>
       <c r="G133" t="n">
@@ -26757,7 +26757,7 @@
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -26767,12 +26767,12 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G134" t="n">
@@ -26801,7 +26801,7 @@
       </c>
       <c r="O134" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P134" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI137"/>
+  <dimension ref="A1:BI127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4885,12 +4885,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5073,7 +5073,7 @@
         <v>0</v>
       </c>
       <c r="BI23" s="3" t="n">
-        <v>46101.5625</v>
+        <v>46101.54166666666</v>
       </c>
     </row>
     <row r="24">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46101.58333333334</v>
+        <v>46101.5625</v>
       </c>
     </row>
     <row r="26">
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5574,10 +5574,10 @@
         <v>0</v>
       </c>
       <c r="AE26" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q28" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.28</v>
+        <v>1.63</v>
       </c>
       <c r="Q30" t="n">
-        <v>5.32</v>
+        <v>3.55</v>
       </c>
       <c r="R30" t="n">
-        <v>8.369999999999999</v>
+        <v>5.55</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9613,12 +9613,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="BI47" s="3" t="n">
-        <v>46101.60416666666</v>
+        <v>46101.58333333334</v>
       </c>
     </row>
     <row r="48">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q49" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R49" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,7 +10209,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>5.88</v>
+        <v>1.58</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R50" t="n">
-        <v>1.73</v>
+        <v>4.96</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10401,12 +10401,12 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="BI51" s="3" t="n">
-        <v>46101.625</v>
+        <v>46101.60416666666</v>
       </c>
     </row>
     <row r="52">
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11189,12 +11189,12 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11377,7 +11377,7 @@
         <v>0</v>
       </c>
       <c r="BI55" s="3" t="n">
-        <v>46101.64583333334</v>
+        <v>46101.625</v>
       </c>
     </row>
     <row r="56">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,7 +12420,7 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P61" t="n">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12814,17 +12814,17 @@
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P63" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q63" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R63" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13159,12 +13159,12 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13347,7 +13347,7 @@
         <v>0</v>
       </c>
       <c r="BI65" s="3" t="n">
-        <v>46101.66666666666</v>
+        <v>46101.64583333334</v>
       </c>
     </row>
     <row r="66">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.41</v>
+        <v>2.88</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="R70" t="n">
-        <v>3.06</v>
+        <v>2.25</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF70" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16705,12 +16705,12 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16893,7 +16893,7 @@
         <v>0</v>
       </c>
       <c r="BI83" s="3" t="n">
-        <v>46101.67708333334</v>
+        <v>46101.66666666666</v>
       </c>
     </row>
     <row r="84">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q84" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R84" t="n">
-        <v>0</v>
+        <v>3.51</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46101.6875</v>
+        <v>46101.67708333334</v>
       </c>
     </row>
     <row r="85">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17794,10 +17794,10 @@
         <v>0</v>
       </c>
       <c r="AG88" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH88" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18872,12 +18872,12 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19060,7 +19060,7 @@
         <v>0</v>
       </c>
       <c r="BI94" s="3" t="n">
-        <v>46101.69791666666</v>
+        <v>46101.6875</v>
       </c>
     </row>
     <row r="95">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="Q96" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R96" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.49</v>
+        <v>3.77</v>
       </c>
       <c r="R97" t="n">
-        <v>2.81</v>
+        <v>2.96</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.36</v>
+        <v>2.17</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.36</v>
+        <v>3.17</v>
       </c>
       <c r="R99" t="n">
-        <v>3.4</v>
+        <v>3.33</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q100" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R100" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.77</v>
+        <v>3.49</v>
       </c>
       <c r="R102" t="n">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>1.35</v>
+        <v>2.84</v>
       </c>
       <c r="Q104" t="n">
-        <v>5.58</v>
+        <v>3.24</v>
       </c>
       <c r="R104" t="n">
-        <v>10.4</v>
+        <v>2.28</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21236,12 +21236,12 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21424,7 +21424,7 @@
         <v>0</v>
       </c>
       <c r="BI106" s="3" t="n">
-        <v>46101.70833333334</v>
+        <v>46101.69791666666</v>
       </c>
     </row>
     <row r="107">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21734,10 +21734,10 @@
         <v>0</v>
       </c>
       <c r="AG108" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21931,10 +21931,10 @@
         <v>0</v>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
@@ -22221,12 +22221,12 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22409,7 +22409,7 @@
         <v>0</v>
       </c>
       <c r="BI111" s="3" t="n">
-        <v>46101.71875</v>
+        <v>46101.70833333334</v>
       </c>
     </row>
     <row r="112">
@@ -22418,27 +22418,27 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46101.85416666666</v>
+        <v>46101.71875</v>
       </c>
     </row>
     <row r="113">
@@ -22615,27 +22615,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Bačka Topola</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Radnički Kragujevac</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.85416666666</v>
       </c>
     </row>
     <row r="114">
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Red Star Belgrade</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Radnički Niš</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,7 +23211,7 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Čukarički</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Železničar Pančevo</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OFK Beograd</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>IMT Novi Beograd</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23802,7 +23802,7 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LFK Mladost Lučani</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Partizan</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Vojvodina</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Napredak</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q122" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R122" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF122" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24979,27 +24979,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.89583333334</v>
       </c>
     </row>
     <row r="126">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
@@ -25191,12 +25191,12 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.95833333334</v>
       </c>
     </row>
     <row r="127">
@@ -25373,12 +25373,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>23:00</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>
@@ -25561,1976 +25561,6 @@
         <v>0</v>
       </c>
       <c r="BI127" s="3" t="n">
-        <v>46101.875</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>Zrinjski</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>Rudar Prijedor</t>
-        </is>
-      </c>
-      <c r="G128" t="n">
-        <v>0</v>
-      </c>
-      <c r="H128" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" t="n">
-        <v>0</v>
-      </c>
-      <c r="J128" t="n">
-        <v>0</v>
-      </c>
-      <c r="K128" t="n">
-        <v>0</v>
-      </c>
-      <c r="L128" t="n">
-        <v>0</v>
-      </c>
-      <c r="M128" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N128" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O128" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q128" t="n">
-        <v>0</v>
-      </c>
-      <c r="R128" t="n">
-        <v>0</v>
-      </c>
-      <c r="S128" t="n">
-        <v>0</v>
-      </c>
-      <c r="T128" t="n">
-        <v>0</v>
-      </c>
-      <c r="U128" t="n">
-        <v>0</v>
-      </c>
-      <c r="V128" t="n">
-        <v>0</v>
-      </c>
-      <c r="W128" t="n">
-        <v>0</v>
-      </c>
-      <c r="X128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y128" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY128" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH128" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI128" s="3" t="n">
-        <v>46101.875</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>Široki Brijeg</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Željezničar</t>
-        </is>
-      </c>
-      <c r="G129" t="n">
-        <v>0</v>
-      </c>
-      <c r="H129" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" t="n">
-        <v>0</v>
-      </c>
-      <c r="J129" t="n">
-        <v>0</v>
-      </c>
-      <c r="K129" t="n">
-        <v>0</v>
-      </c>
-      <c r="L129" t="n">
-        <v>0</v>
-      </c>
-      <c r="M129" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N129" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O129" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
-      <c r="R129" t="n">
-        <v>0</v>
-      </c>
-      <c r="S129" t="n">
-        <v>0</v>
-      </c>
-      <c r="T129" t="n">
-        <v>0</v>
-      </c>
-      <c r="U129" t="n">
-        <v>0</v>
-      </c>
-      <c r="V129" t="n">
-        <v>0</v>
-      </c>
-      <c r="W129" t="n">
-        <v>0</v>
-      </c>
-      <c r="X129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y129" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY129" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH129" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI129" s="3" t="n">
-        <v>46101.875</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Bosnia and Herzegovina Premier League of Bosnia</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>Sarajevo</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Velež</t>
-        </is>
-      </c>
-      <c r="G130" t="n">
-        <v>0</v>
-      </c>
-      <c r="H130" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" t="n">
-        <v>0</v>
-      </c>
-      <c r="J130" t="n">
-        <v>0</v>
-      </c>
-      <c r="K130" t="n">
-        <v>0</v>
-      </c>
-      <c r="L130" t="n">
-        <v>0</v>
-      </c>
-      <c r="M130" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N130" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O130" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
-      <c r="R130" t="n">
-        <v>0</v>
-      </c>
-      <c r="S130" t="n">
-        <v>0</v>
-      </c>
-      <c r="T130" t="n">
-        <v>0</v>
-      </c>
-      <c r="U130" t="n">
-        <v>0</v>
-      </c>
-      <c r="V130" t="n">
-        <v>0</v>
-      </c>
-      <c r="W130" t="n">
-        <v>0</v>
-      </c>
-      <c r="X130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y130" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY130" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH130" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI130" s="3" t="n">
-        <v>46101.875</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>Mačva Šabac</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Dubočica</t>
-        </is>
-      </c>
-      <c r="G131" t="n">
-        <v>0</v>
-      </c>
-      <c r="H131" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" t="n">
-        <v>0</v>
-      </c>
-      <c r="J131" t="n">
-        <v>0</v>
-      </c>
-      <c r="K131" t="n">
-        <v>0</v>
-      </c>
-      <c r="L131" t="n">
-        <v>0</v>
-      </c>
-      <c r="M131" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N131" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O131" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q131" t="n">
-        <v>0</v>
-      </c>
-      <c r="R131" t="n">
-        <v>0</v>
-      </c>
-      <c r="S131" t="n">
-        <v>0</v>
-      </c>
-      <c r="T131" t="n">
-        <v>0</v>
-      </c>
-      <c r="U131" t="n">
-        <v>0</v>
-      </c>
-      <c r="V131" t="n">
-        <v>0</v>
-      </c>
-      <c r="W131" t="n">
-        <v>0</v>
-      </c>
-      <c r="X131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y131" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY131" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH131" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI131" s="3" t="n">
-        <v>46101.875</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Serbia Prva Liga</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>Tekstilac Odžaci</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Trajal Krusevac</t>
-        </is>
-      </c>
-      <c r="G132" t="n">
-        <v>0</v>
-      </c>
-      <c r="H132" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" t="n">
-        <v>0</v>
-      </c>
-      <c r="J132" t="n">
-        <v>0</v>
-      </c>
-      <c r="K132" t="n">
-        <v>0</v>
-      </c>
-      <c r="L132" t="n">
-        <v>0</v>
-      </c>
-      <c r="M132" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N132" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q132" t="n">
-        <v>0</v>
-      </c>
-      <c r="R132" t="n">
-        <v>0</v>
-      </c>
-      <c r="S132" t="n">
-        <v>0</v>
-      </c>
-      <c r="T132" t="n">
-        <v>0</v>
-      </c>
-      <c r="U132" t="n">
-        <v>0</v>
-      </c>
-      <c r="V132" t="n">
-        <v>0</v>
-      </c>
-      <c r="W132" t="n">
-        <v>0</v>
-      </c>
-      <c r="X132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y132" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY132" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH132" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI132" s="3" t="n">
-        <v>46101.875</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>Serbia SuperLiga</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>Javor Ivanjica</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Novi Pazar</t>
-        </is>
-      </c>
-      <c r="G133" t="n">
-        <v>0</v>
-      </c>
-      <c r="H133" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" t="n">
-        <v>0</v>
-      </c>
-      <c r="J133" t="n">
-        <v>0</v>
-      </c>
-      <c r="K133" t="n">
-        <v>0</v>
-      </c>
-      <c r="L133" t="n">
-        <v>0</v>
-      </c>
-      <c r="M133" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N133" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O133" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
-      <c r="R133" t="n">
-        <v>0</v>
-      </c>
-      <c r="S133" t="n">
-        <v>0</v>
-      </c>
-      <c r="T133" t="n">
-        <v>0</v>
-      </c>
-      <c r="U133" t="n">
-        <v>0</v>
-      </c>
-      <c r="V133" t="n">
-        <v>0</v>
-      </c>
-      <c r="W133" t="n">
-        <v>0</v>
-      </c>
-      <c r="X133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y133" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY133" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH133" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI133" s="3" t="n">
-        <v>46101.875</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>21:00</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Slovenia PrvaLiga</t>
-        </is>
-      </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>Domžale</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Koper</t>
-        </is>
-      </c>
-      <c r="G134" t="n">
-        <v>0</v>
-      </c>
-      <c r="H134" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" t="n">
-        <v>0</v>
-      </c>
-      <c r="J134" t="n">
-        <v>0</v>
-      </c>
-      <c r="K134" t="n">
-        <v>0</v>
-      </c>
-      <c r="L134" t="n">
-        <v>0</v>
-      </c>
-      <c r="M134" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N134" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O134" t="inlineStr">
-        <is>
-          <t>canceled</t>
-        </is>
-      </c>
-      <c r="P134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
-      <c r="R134" t="n">
-        <v>0</v>
-      </c>
-      <c r="S134" t="n">
-        <v>0</v>
-      </c>
-      <c r="T134" t="n">
-        <v>0</v>
-      </c>
-      <c r="U134" t="n">
-        <v>0</v>
-      </c>
-      <c r="V134" t="n">
-        <v>0</v>
-      </c>
-      <c r="W134" t="n">
-        <v>0</v>
-      </c>
-      <c r="X134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y134" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY134" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH134" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI134" s="3" t="n">
-        <v>46101.875</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>21:30</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Argentina Prim B Nacional</t>
-        </is>
-      </c>
-      <c r="D135" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>San Martín San Juan</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>San Martín Tucumán</t>
-        </is>
-      </c>
-      <c r="G135" t="n">
-        <v>0</v>
-      </c>
-      <c r="H135" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" t="n">
-        <v>0</v>
-      </c>
-      <c r="J135" t="n">
-        <v>0</v>
-      </c>
-      <c r="K135" t="n">
-        <v>0</v>
-      </c>
-      <c r="L135" t="n">
-        <v>0</v>
-      </c>
-      <c r="M135" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N135" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O135" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
-      <c r="R135" t="n">
-        <v>0</v>
-      </c>
-      <c r="S135" t="n">
-        <v>0</v>
-      </c>
-      <c r="T135" t="n">
-        <v>0</v>
-      </c>
-      <c r="U135" t="n">
-        <v>0</v>
-      </c>
-      <c r="V135" t="n">
-        <v>0</v>
-      </c>
-      <c r="W135" t="n">
-        <v>0</v>
-      </c>
-      <c r="X135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y135" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY135" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH135" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI135" s="3" t="n">
-        <v>46101.89583333334</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>USA NWSL</t>
-        </is>
-      </c>
-      <c r="D136" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Portland Thorns</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Seattle Reign</t>
-        </is>
-      </c>
-      <c r="G136" t="n">
-        <v>0</v>
-      </c>
-      <c r="H136" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" t="n">
-        <v>0</v>
-      </c>
-      <c r="J136" t="n">
-        <v>0</v>
-      </c>
-      <c r="K136" t="n">
-        <v>0</v>
-      </c>
-      <c r="L136" t="n">
-        <v>0</v>
-      </c>
-      <c r="M136" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N136" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
-      <c r="R136" t="n">
-        <v>0</v>
-      </c>
-      <c r="S136" t="n">
-        <v>0</v>
-      </c>
-      <c r="T136" t="n">
-        <v>0</v>
-      </c>
-      <c r="U136" t="n">
-        <v>0</v>
-      </c>
-      <c r="V136" t="n">
-        <v>0</v>
-      </c>
-      <c r="W136" t="n">
-        <v>0</v>
-      </c>
-      <c r="X136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y136" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY136" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH136" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI136" s="3" t="n">
-        <v>46101.95833333334</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" s="2" t="n">
-        <v>46101</v>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>23:00</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Australia A-League</t>
-        </is>
-      </c>
-      <c r="D137" t="inlineStr">
-        <is>
-          <t>2025/2026</t>
-        </is>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>Auckland</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Macarthur</t>
-        </is>
-      </c>
-      <c r="G137" t="n">
-        <v>0</v>
-      </c>
-      <c r="H137" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" t="n">
-        <v>0</v>
-      </c>
-      <c r="J137" t="n">
-        <v>0</v>
-      </c>
-      <c r="K137" t="n">
-        <v>0</v>
-      </c>
-      <c r="L137" t="n">
-        <v>0</v>
-      </c>
-      <c r="M137" t="n">
-        <v>-1</v>
-      </c>
-      <c r="N137" t="n">
-        <v>-1</v>
-      </c>
-      <c r="O137" t="inlineStr">
-        <is>
-          <t>incomplete</t>
-        </is>
-      </c>
-      <c r="P137" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="Q137" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="R137" t="n">
-        <v>5.38</v>
-      </c>
-      <c r="S137" t="n">
-        <v>0</v>
-      </c>
-      <c r="T137" t="n">
-        <v>0</v>
-      </c>
-      <c r="U137" t="n">
-        <v>0</v>
-      </c>
-      <c r="V137" t="n">
-        <v>0</v>
-      </c>
-      <c r="W137" t="n">
-        <v>0</v>
-      </c>
-      <c r="X137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y137" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY137" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH137" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI137" s="3" t="n">
         <v>46101.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2574,13 +2574,13 @@
         </is>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>3.57</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R25" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,22 +5481,22 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -5923,13 +5923,13 @@
         </is>
       </c>
       <c r="P28" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R28" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S28" t="n">
         <v>0</v>
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.77</v>
+        <v>2.22</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>4.09</v>
+        <v>2.92</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.28</v>
+        <v>1.77</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.32</v>
+        <v>3.8</v>
       </c>
       <c r="R41" t="n">
-        <v>8.369999999999999</v>
+        <v>4.09</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF41" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.54</v>
+        <v>1.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.2</v>
+        <v>5.32</v>
       </c>
       <c r="R42" t="n">
-        <v>5.37</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q45" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R45" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF45" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.14</v>
+        <v>3.56</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>3.35</v>
+        <v>2.1</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,7 +12026,7 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P59" t="n">
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.56</v>
+        <v>2.45</v>
       </c>
       <c r="Q60" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>2.1</v>
+        <v>2.75</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>4</v>
+        <v>2.14</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="R63" t="n">
-        <v>1.77</v>
+        <v>3.35</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.85</v>
+        <v>2.28</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R64" t="n">
-        <v>2.02</v>
+        <v>3.46</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.54</v>
+        <v>3.6</v>
       </c>
       <c r="R69" t="n">
-        <v>3.5</v>
+        <v>2.98</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="R70" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14242,10 +14242,10 @@
         <v>0</v>
       </c>
       <c r="AE70" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF70" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.34</v>
+        <v>2.88</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.05</v>
+        <v>3.34</v>
       </c>
       <c r="R72" t="n">
-        <v>3.21</v>
+        <v>2.25</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.41</v>
+        <v>2.67</v>
       </c>
       <c r="Q75" t="n">
         <v>3.08</v>
       </c>
       <c r="R75" t="n">
-        <v>3.06</v>
+        <v>2.69</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.67</v>
+        <v>2.36</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.08</v>
+        <v>3.7</v>
       </c>
       <c r="R83" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.4</v>
+        <v>1.96</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.5</v>
+        <v>4.16</v>
       </c>
       <c r="R90" t="n">
-        <v>2.65</v>
+        <v>3.78</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>4.67</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.1</v>
+        <v>2.36</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.77</v>
+        <v>3.36</v>
       </c>
       <c r="R97" t="n">
-        <v>2.96</v>
+        <v>3.4</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>1.35</v>
+        <v>5.38</v>
       </c>
       <c r="Q98" t="n">
-        <v>5.58</v>
+        <v>3.52</v>
       </c>
       <c r="R98" t="n">
-        <v>10.4</v>
+        <v>1.59</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.17</v>
+        <v>2.3</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.17</v>
+        <v>3.49</v>
       </c>
       <c r="R99" t="n">
-        <v>3.33</v>
+        <v>2.81</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.42</v>
+        <v>2.17</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.22</v>
+        <v>3.17</v>
       </c>
       <c r="R100" t="n">
-        <v>2.87</v>
+        <v>3.33</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.3</v>
+        <v>2.42</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.49</v>
+        <v>3.22</v>
       </c>
       <c r="R102" t="n">
-        <v>2.81</v>
+        <v>2.87</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>5.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.52</v>
+        <v>3.77</v>
       </c>
       <c r="R103" t="n">
-        <v>1.59</v>
+        <v>2.96</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R106" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21734,10 +21734,10 @@
         <v>0</v>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>3.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.22</v>
+        <v>3.13</v>
       </c>
       <c r="R109" t="n">
-        <v>2.07</v>
+        <v>2.88</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,16 +21925,16 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG109" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23408,7 +23408,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q118" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R118" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF118" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,22 +24393,22 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24441,13 +24441,13 @@
         </is>
       </c>
       <c r="P122" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q122" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R122" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S122" t="n">
         <v>0</v>
@@ -24486,10 +24486,10 @@
         <v>0</v>
       </c>
       <c r="AE122" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF122" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG122" t="n">
         <v>0</v>
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R127" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.63</v>
+        <v>1.28</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.55</v>
+        <v>5.32</v>
       </c>
       <c r="R37" t="n">
-        <v>5.55</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8529,10 +8529,10 @@
         <v>0</v>
       </c>
       <c r="AE41" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF41" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,22 +8830,22 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,22 +9027,22 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.81</v>
+        <v>2.22</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="R45" t="n">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9317,10 +9317,10 @@
         <v>0</v>
       </c>
       <c r="AE45" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF45" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.54</v>
+        <v>2.2</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.2</v>
+        <v>3.3</v>
       </c>
       <c r="R47" t="n">
-        <v>5.37</v>
+        <v>3.17</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>5.88</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>5.88</v>
+        <v>1.58</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R49" t="n">
-        <v>1.73</v>
+        <v>4.96</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10219,12 +10219,12 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R50" t="n">
-        <v>4.96</v>
+        <v>3.26</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R51" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R54" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.56</v>
+        <v>4</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>3.76</v>
       </c>
       <c r="R56" t="n">
-        <v>2.1</v>
+        <v>1.77</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.55</v>
+        <v>3.32</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="R57" t="n">
-        <v>2.02</v>
+        <v>2.05</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="R58" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,17 +12026,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>4</v>
+        <v>2.28</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.76</v>
+        <v>2.75</v>
       </c>
       <c r="R61" t="n">
-        <v>1.77</v>
+        <v>3.46</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,14 +13015,14 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.28</v>
+        <v>2.45</v>
       </c>
       <c r="Q64" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="R64" t="n">
         <v>2.75</v>
       </c>
-      <c r="R64" t="n">
-        <v>3.46</v>
-      </c>
       <c r="S64" t="n">
         <v>0</v>
       </c>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF64" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,22 +13164,22 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,7 +13208,7 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P65" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.7</v>
+        <v>2.12</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.28</v>
+        <v>3.6</v>
       </c>
       <c r="R66" t="n">
-        <v>2.52</v>
+        <v>2.98</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.88</v>
+        <v>2.7</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.54</v>
+        <v>3.28</v>
       </c>
       <c r="R71" t="n">
-        <v>3.5</v>
+        <v>2.52</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.34</v>
+        <v>3.62</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="R73" t="n">
-        <v>3.21</v>
+        <v>2.03</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="R75" t="n">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.7</v>
+        <v>3.05</v>
       </c>
       <c r="R83" t="n">
-        <v>2.88</v>
+        <v>3.21</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="R88" t="n">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="R92" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH93" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>6.01</v>
+        <v>2.3</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.1</v>
+        <v>3.49</v>
       </c>
       <c r="R96" t="n">
-        <v>1.45</v>
+        <v>2.81</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.3</v>
+        <v>2.84</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.49</v>
+        <v>3.24</v>
       </c>
       <c r="R99" t="n">
-        <v>2.81</v>
+        <v>2.28</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.17</v>
+        <v>2.36</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.17</v>
+        <v>3.36</v>
       </c>
       <c r="R100" t="n">
-        <v>3.33</v>
+        <v>3.4</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>4.67</v>
+        <v>6.01</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.74</v>
+        <v>4.1</v>
       </c>
       <c r="R101" t="n">
-        <v>1.62</v>
+        <v>1.45</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.42</v>
+        <v>4.67</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.22</v>
+        <v>3.74</v>
       </c>
       <c r="R102" t="n">
-        <v>2.87</v>
+        <v>1.62</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,7 +20650,7 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R103" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.84</v>
+        <v>2.42</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.24</v>
+        <v>3.22</v>
       </c>
       <c r="R104" t="n">
-        <v>2.28</v>
+        <v>2.87</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF104" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>1.35</v>
+        <v>2.1</v>
       </c>
       <c r="Q105" t="n">
-        <v>5.58</v>
+        <v>3.77</v>
       </c>
       <c r="R105" t="n">
-        <v>10.4</v>
+        <v>2.96</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Q106" t="n">
-        <v>0</v>
+        <v>5.58</v>
       </c>
       <c r="R106" t="n">
-        <v>0</v>
+        <v>10.4</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23452,7 +23452,7 @@
       </c>
       <c r="O117" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P117" t="n">
@@ -23605,22 +23605,22 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23653,13 +23653,13 @@
         </is>
       </c>
       <c r="P118" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q118" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R118" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S118" t="n">
         <v>0</v>
@@ -23698,10 +23698,10 @@
         <v>0</v>
       </c>
       <c r="AE118" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF118" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG118" t="n">
         <v>0</v>
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q119" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R119" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF119" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,22 +6072,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>2.81</v>
+        <v>1.77</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>2.32</v>
+        <v>4.09</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9272,13 +9272,13 @@
         </is>
       </c>
       <c r="P45" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R45" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S45" t="n">
         <v>0</v>
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q46" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R46" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.2</v>
+        <v>1.54</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="R47" t="n">
-        <v>3.17</v>
+        <v>5.37</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,7 +9815,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>5.88</v>
+        <v>2.01</v>
       </c>
       <c r="Q48" t="n">
         <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>1.73</v>
+        <v>3.26</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.58</v>
+        <v>5.88</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R49" t="n">
-        <v>4.96</v>
+        <v>1.73</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,22 +10406,22 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q51" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R51" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.76</v>
+        <v>0</v>
       </c>
       <c r="R56" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R58" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.56</v>
+        <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R59" t="n">
-        <v>2.1</v>
+        <v>3.46</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.28</v>
+        <v>3.32</v>
       </c>
       <c r="Q61" t="n">
-        <v>2.75</v>
+        <v>3.66</v>
       </c>
       <c r="R61" t="n">
-        <v>3.46</v>
+        <v>2.05</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.14</v>
+        <v>2.45</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.1</v>
+        <v>3.2</v>
       </c>
       <c r="R63" t="n">
-        <v>3.35</v>
+        <v>2.75</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.45</v>
+        <v>2.14</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R64" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13060,10 +13060,10 @@
         <v>0</v>
       </c>
       <c r="AE64" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF64" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.67</v>
+        <v>1.88</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="R67" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.36</v>
+        <v>2.48</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.7</v>
+        <v>3.36</v>
       </c>
       <c r="R68" t="n">
-        <v>2.88</v>
+        <v>2.69</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.93</v>
+        <v>2.41</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="R70" t="n">
-        <v>2.04</v>
+        <v>3.06</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="R71" t="n">
-        <v>2.52</v>
+        <v>2.03</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.41</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>3.06</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.48</v>
+        <v>2.34</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.36</v>
+        <v>3.05</v>
       </c>
       <c r="R80" t="n">
-        <v>2.69</v>
+        <v>3.21</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.34</v>
+        <v>2.7</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.05</v>
+        <v>3.28</v>
       </c>
       <c r="R83" t="n">
-        <v>3.21</v>
+        <v>2.52</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="R88" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH90" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18779,10 +18779,10 @@
         <v>0</v>
       </c>
       <c r="AG93" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH93" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,22 +19074,22 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="R95" t="n">
-        <v>3.33</v>
+        <v>2.87</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,22 +19271,22 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.49</v>
+        <v>5.58</v>
       </c>
       <c r="R96" t="n">
-        <v>2.81</v>
+        <v>10.4</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF97" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>5.38</v>
+        <v>2.17</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.52</v>
+        <v>3.17</v>
       </c>
       <c r="R98" t="n">
-        <v>1.59</v>
+        <v>3.33</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.84</v>
+        <v>4.67</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.24</v>
+        <v>3.74</v>
       </c>
       <c r="R99" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.36</v>
+        <v>2.3</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.36</v>
+        <v>3.49</v>
       </c>
       <c r="R100" t="n">
-        <v>3.4</v>
+        <v>2.81</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,7 +20453,7 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>4.67</v>
+        <v>2.84</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.74</v>
+        <v>3.24</v>
       </c>
       <c r="R102" t="n">
-        <v>1.62</v>
+        <v>2.28</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.79</v>
+        <v>1.93</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.97</v>
+        <v>1.83</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="R104" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.1</v>
+        <v>6.01</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="R105" t="n">
-        <v>2.96</v>
+        <v>1.45</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>1.35</v>
+        <v>5.38</v>
       </c>
       <c r="Q106" t="n">
-        <v>5.58</v>
+        <v>3.52</v>
       </c>
       <c r="R106" t="n">
-        <v>10.4</v>
+        <v>1.59</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>3.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.22</v>
+        <v>3.13</v>
       </c>
       <c r="R108" t="n">
-        <v>2.07</v>
+        <v>2.88</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,16 +21728,16 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG108" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q110" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R110" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22128,10 +22128,10 @@
         <v>0</v>
       </c>
       <c r="AG110" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH110" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23802,22 +23802,22 @@
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23850,13 +23850,13 @@
         </is>
       </c>
       <c r="P119" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q119" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R119" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S119" t="n">
         <v>0</v>
@@ -23895,10 +23895,10 @@
         <v>0</v>
       </c>
       <c r="AE119" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF119" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG119" t="n">
         <v>0</v>
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q123" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R123" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF123" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>4.4</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Q127" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R127" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1392,13 +1392,13 @@
         </is>
       </c>
       <c r="P5" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1551,12 +1551,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,7 +4693,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -4703,12 +4703,12 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.81</v>
+        <v>1.77</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.46</v>
+        <v>3.8</v>
       </c>
       <c r="R29" t="n">
-        <v>2.32</v>
+        <v>4.09</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.99</v>
+        <v>1.76</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.78</v>
+        <v>1.96</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>2.2</v>
+        <v>1.28</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.3</v>
+        <v>5.32</v>
       </c>
       <c r="R42" t="n">
-        <v>3.17</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9421,7 +9421,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -9431,12 +9431,12 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>1.63</v>
+        <v>2.22</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="R46" t="n">
-        <v>5.55</v>
+        <v>2.92</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>5.88</v>
+        <v>1.58</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R49" t="n">
-        <v>1.73</v>
+        <v>4.96</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.58</v>
+        <v>5.88</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>4.96</v>
+        <v>1.73</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11435,17 +11435,17 @@
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="Q56" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R56" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,22 +11588,22 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>3.56</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R58" t="n">
-        <v>2.1</v>
+        <v>3.35</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.28</v>
+        <v>3.85</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="R59" t="n">
-        <v>3.46</v>
+        <v>2.02</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.55</v>
+        <v>2.45</v>
       </c>
       <c r="Q60" t="n">
         <v>3.2</v>
       </c>
       <c r="R60" t="n">
-        <v>2.02</v>
+        <v>2.75</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF60" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.32</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.66</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.05</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.85</v>
+        <v>2.28</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R62" t="n">
-        <v>2.02</v>
+        <v>3.46</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.45</v>
+        <v>3.32</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.2</v>
+        <v>3.66</v>
       </c>
       <c r="R63" t="n">
-        <v>2.75</v>
+        <v>2.05</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12863,10 +12863,10 @@
         <v>0</v>
       </c>
       <c r="AE63" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF63" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG63" t="n">
         <v>0</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,17 +13011,17 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P64" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>4</v>
+        <v>3.56</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>1.77</v>
+        <v>2.1</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.12</v>
+        <v>2.7</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.6</v>
+        <v>3.28</v>
       </c>
       <c r="R66" t="n">
-        <v>2.98</v>
+        <v>2.52</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.48</v>
+        <v>2.41</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.36</v>
+        <v>3.08</v>
       </c>
       <c r="R68" t="n">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13848,10 +13848,10 @@
         <v>0</v>
       </c>
       <c r="AE68" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF68" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF69" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="R70" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R76" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.34</v>
+        <v>2.93</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.05</v>
+        <v>3.74</v>
       </c>
       <c r="R80" t="n">
-        <v>3.21</v>
+        <v>2.04</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.7</v>
+        <v>2.48</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.28</v>
+        <v>3.36</v>
       </c>
       <c r="R83" t="n">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.5</v>
+        <v>2.72</v>
       </c>
       <c r="R87" t="n">
-        <v>2.65</v>
+        <v>3.35</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18188,10 +18188,10 @@
         <v>0</v>
       </c>
       <c r="AG90" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.42</v>
+        <v>2.36</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.22</v>
+        <v>3.36</v>
       </c>
       <c r="R95" t="n">
-        <v>2.87</v>
+        <v>3.4</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>1.35</v>
+        <v>2.42</v>
       </c>
       <c r="Q96" t="n">
-        <v>5.58</v>
+        <v>3.22</v>
       </c>
       <c r="R96" t="n">
-        <v>10.4</v>
+        <v>2.87</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.77</v>
+        <v>3.17</v>
       </c>
       <c r="R97" t="n">
-        <v>2.96</v>
+        <v>3.33</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19561,10 +19561,10 @@
         <v>0</v>
       </c>
       <c r="AE97" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF97" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.17</v>
+        <v>3.77</v>
       </c>
       <c r="R98" t="n">
-        <v>3.33</v>
+        <v>2.96</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF98" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>4.67</v>
+        <v>1.35</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.74</v>
+        <v>5.58</v>
       </c>
       <c r="R99" t="n">
-        <v>1.62</v>
+        <v>10.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -19955,10 +19955,10 @@
         <v>0</v>
       </c>
       <c r="AE99" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF99" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.3</v>
+        <v>5.38</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="R100" t="n">
-        <v>2.81</v>
+        <v>1.59</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>6.01</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.84</v>
+        <v>2.3</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.24</v>
+        <v>3.49</v>
       </c>
       <c r="R102" t="n">
-        <v>2.28</v>
+        <v>2.81</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>6.01</v>
+        <v>2.84</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="R105" t="n">
-        <v>1.45</v>
+        <v>2.28</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>5.38</v>
+        <v>4.67</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.52</v>
+        <v>3.74</v>
       </c>
       <c r="R106" t="n">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R108" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,22 +21832,22 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,7 +23014,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23058,7 +23058,7 @@
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G121" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,22 +1738,22 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1983,13 +1983,13 @@
         </is>
       </c>
       <c r="P8" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4786,10 +4786,10 @@
         <v>0</v>
       </c>
       <c r="AE22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG22" t="n">
         <v>0</v>
@@ -4890,22 +4890,22 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>2.2</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="R26" t="n">
-        <v>3.17</v>
+        <v>5.55</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,22 +5678,22 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.8</v>
+        <v>3.3</v>
       </c>
       <c r="R29" t="n">
-        <v>4.09</v>
+        <v>3.17</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6165,10 +6165,10 @@
         <v>0</v>
       </c>
       <c r="AE29" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF29" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,13 +6317,13 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R30" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S30" t="n">
         <v>0</v>
@@ -6362,10 +6362,10 @@
         <v>0</v>
       </c>
       <c r="AE30" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF30" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG30" t="n">
         <v>0</v>
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R33" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -6953,10 +6953,10 @@
         <v>0</v>
       </c>
       <c r="AE33" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF33" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,7 +7451,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF36" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q41" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R41" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9469,13 +9469,13 @@
         </is>
       </c>
       <c r="P46" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R46" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S46" t="n">
         <v>0</v>
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="R56" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R57" t="n">
-        <v>2.02</v>
+        <v>3.35</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R58" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>2.45</v>
+        <v>3.56</v>
       </c>
       <c r="Q60" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R60" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12272,10 +12272,10 @@
         <v>0</v>
       </c>
       <c r="AE60" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF60" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG60" t="n">
         <v>0</v>
@@ -12376,22 +12376,22 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="Q62" t="n">
-        <v>2.75</v>
+        <v>3.76</v>
       </c>
       <c r="R62" t="n">
-        <v>3.46</v>
+        <v>1.77</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="R63" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.56</v>
+        <v>3.32</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>3.66</v>
       </c>
       <c r="R65" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.7</v>
+        <v>1.88</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.28</v>
+        <v>3.54</v>
       </c>
       <c r="R66" t="n">
-        <v>2.52</v>
+        <v>3.5</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.41</v>
+        <v>2.12</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="R68" t="n">
-        <v>3.06</v>
+        <v>2.98</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14045,10 +14045,10 @@
         <v>0</v>
       </c>
       <c r="AE69" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF69" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.05</v>
+        <v>3.7</v>
       </c>
       <c r="R70" t="n">
-        <v>3.21</v>
+        <v>2.88</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R72" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R73" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.62</v>
+        <v>2.34</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="R74" t="n">
-        <v>2.03</v>
+        <v>3.21</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>0</v>
+        <v>3.62</v>
       </c>
       <c r="Q75" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R75" t="n">
-        <v>0</v>
+        <v>2.03</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.67</v>
+        <v>2.41</v>
       </c>
       <c r="Q77" t="n">
         <v>3.08</v>
       </c>
       <c r="R77" t="n">
-        <v>2.69</v>
+        <v>3.06</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF79" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.93</v>
+        <v>2.67</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="R80" t="n">
-        <v>2.04</v>
+        <v>2.69</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17203,10 +17203,10 @@
         <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH85" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>1.96</v>
+        <v>2.4</v>
       </c>
       <c r="Q86" t="n">
-        <v>4.16</v>
+        <v>3.5</v>
       </c>
       <c r="R86" t="n">
-        <v>3.78</v>
+        <v>2.65</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17400,10 +17400,10 @@
         <v>0</v>
       </c>
       <c r="AG86" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH86" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.36</v>
+        <v>2.42</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.36</v>
+        <v>3.22</v>
       </c>
       <c r="R95" t="n">
-        <v>3.4</v>
+        <v>2.87</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.42</v>
+        <v>6.01</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.22</v>
+        <v>4.1</v>
       </c>
       <c r="R96" t="n">
-        <v>2.87</v>
+        <v>1.45</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.17</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>3.33</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.35</v>
+        <v>2.17</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.58</v>
+        <v>3.17</v>
       </c>
       <c r="R99" t="n">
-        <v>10.4</v>
+        <v>3.33</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>5.38</v>
+        <v>1.35</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.52</v>
+        <v>5.58</v>
       </c>
       <c r="R100" t="n">
-        <v>1.59</v>
+        <v>10.4</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>6.01</v>
+        <v>2.36</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="R101" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.3</v>
+        <v>5.38</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.49</v>
+        <v>3.52</v>
       </c>
       <c r="R102" t="n">
-        <v>2.81</v>
+        <v>1.59</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>0</v>
+        <v>4.67</v>
       </c>
       <c r="Q103" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R103" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>4.67</v>
+        <v>2.3</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.74</v>
+        <v>3.49</v>
       </c>
       <c r="R106" t="n">
-        <v>1.62</v>
+        <v>2.81</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF107" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.48</v>
+        <v>3.38</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.13</v>
+        <v>4.22</v>
       </c>
       <c r="R109" t="n">
-        <v>2.88</v>
+        <v>2.07</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,16 +21925,16 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH109" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
@@ -22029,22 +22029,22 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22077,13 +22077,13 @@
         </is>
       </c>
       <c r="P110" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q110" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R110" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S110" t="n">
         <v>0</v>
@@ -22128,10 +22128,10 @@
         <v>0</v>
       </c>
       <c r="AG110" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH110" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI110" t="n">
         <v>0</v>
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23221,12 +23221,12 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24638,13 +24638,13 @@
         </is>
       </c>
       <c r="P123" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q123" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R123" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S123" t="n">
         <v>0</v>
@@ -24683,10 +24683,10 @@
         <v>0</v>
       </c>
       <c r="AE123" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF123" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG123" t="n">
         <v>0</v>
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q124" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R124" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF124" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3511,22 +3511,22 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R16" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3708,22 +3708,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3756,13 +3756,13 @@
         </is>
       </c>
       <c r="P17" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="S17" t="n">
         <v>0</v>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>4.66</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R26" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,13 +6120,13 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R29" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,22 +7254,22 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7544,10 +7544,10 @@
         <v>0</v>
       </c>
       <c r="AE36" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF36" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF37" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.28</v>
+        <v>2.2</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.32</v>
+        <v>3.3</v>
       </c>
       <c r="R39" t="n">
-        <v>8.369999999999999</v>
+        <v>3.17</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q40" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R40" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF40" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10012,7 +10012,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>1.58</v>
+        <v>5.88</v>
       </c>
       <c r="Q49" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R49" t="n">
-        <v>4.96</v>
+        <v>1.73</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>5.88</v>
+        <v>1.58</v>
       </c>
       <c r="Q51" t="n">
-        <v>3.75</v>
+        <v>4.1</v>
       </c>
       <c r="R51" t="n">
-        <v>1.73</v>
+        <v>4.96</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,13 +11242,13 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R55" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S55" t="n">
         <v>0</v>
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,10 +11439,10 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="Q56" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R56" t="n">
         <v>2.02</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.14</v>
+        <v>4</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.1</v>
+        <v>3.76</v>
       </c>
       <c r="R57" t="n">
-        <v>3.35</v>
+        <v>1.77</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.28</v>
+        <v>2.14</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.75</v>
+        <v>3.1</v>
       </c>
       <c r="R58" t="n">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,22 +11982,22 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q59" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R59" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R61" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12469,10 +12469,10 @@
         <v>0</v>
       </c>
       <c r="AE61" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF61" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>4</v>
+        <v>2.45</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.76</v>
+        <v>3.2</v>
       </c>
       <c r="R62" t="n">
-        <v>1.77</v>
+        <v>2.75</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.55</v>
+        <v>2.28</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.2</v>
+        <v>2.75</v>
       </c>
       <c r="R63" t="n">
-        <v>2.02</v>
+        <v>3.46</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13011,7 +13011,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P64" t="n">
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>1.88</v>
+        <v>2.67</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.54</v>
+        <v>3.08</v>
       </c>
       <c r="R66" t="n">
-        <v>3.5</v>
+        <v>2.69</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13454,10 +13454,10 @@
         <v>0</v>
       </c>
       <c r="AE66" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF66" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,14 +13606,14 @@
         </is>
       </c>
       <c r="P67" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="Q67" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="R67" t="n">
         <v>2.88</v>
       </c>
-      <c r="Q67" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="R67" t="n">
-        <v>2.25</v>
-      </c>
       <c r="S67" t="n">
         <v>0</v>
       </c>
@@ -13651,10 +13651,10 @@
         <v>0</v>
       </c>
       <c r="AE67" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF67" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.36</v>
+        <v>2.41</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="R70" t="n">
-        <v>2.88</v>
+        <v>3.06</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R74" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.62</v>
+        <v>2.34</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="R75" t="n">
-        <v>2.03</v>
+        <v>3.21</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q76" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R76" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.41</v>
+        <v>2.48</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.08</v>
+        <v>3.36</v>
       </c>
       <c r="R77" t="n">
-        <v>3.06</v>
+        <v>2.69</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R78" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.48</v>
+        <v>3.62</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="R79" t="n">
-        <v>2.69</v>
+        <v>2.03</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16015,10 +16015,10 @@
         <v>0</v>
       </c>
       <c r="AE79" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF79" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>2.67</v>
+        <v>1.88</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.08</v>
+        <v>3.54</v>
       </c>
       <c r="R80" t="n">
-        <v>2.69</v>
+        <v>3.5</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17203,10 +17203,10 @@
         <v>0</v>
       </c>
       <c r="AG85" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH85" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI85" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF87" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q91" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R91" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH91" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.46</v>
+        <v>2.02</v>
       </c>
       <c r="Q92" t="n">
-        <v>2.72</v>
+        <v>3.45</v>
       </c>
       <c r="R92" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R95" t="n">
-        <v>2.87</v>
+        <v>2.28</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>6.01</v>
+        <v>2.36</v>
       </c>
       <c r="Q96" t="n">
-        <v>4.1</v>
+        <v>3.36</v>
       </c>
       <c r="R96" t="n">
-        <v>1.45</v>
+        <v>3.4</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.49</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,7 +19665,7 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.77</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.96</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19758,10 +19758,10 @@
         <v>0</v>
       </c>
       <c r="AE98" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>2.17</v>
+        <v>1.35</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.17</v>
+        <v>5.58</v>
       </c>
       <c r="R99" t="n">
-        <v>3.33</v>
+        <v>10.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>1.35</v>
+        <v>2.42</v>
       </c>
       <c r="Q100" t="n">
-        <v>5.58</v>
+        <v>3.22</v>
       </c>
       <c r="R100" t="n">
-        <v>10.4</v>
+        <v>2.87</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R101" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>5.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.52</v>
+        <v>3.77</v>
       </c>
       <c r="R102" t="n">
-        <v>1.59</v>
+        <v>2.96</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF102" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>4.67</v>
+        <v>2.17</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.74</v>
+        <v>3.17</v>
       </c>
       <c r="R103" t="n">
-        <v>1.62</v>
+        <v>3.33</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.84</v>
+        <v>6.01</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.24</v>
+        <v>4.1</v>
       </c>
       <c r="R105" t="n">
-        <v>2.28</v>
+        <v>1.45</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.3</v>
+        <v>4.67</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.49</v>
+        <v>3.74</v>
       </c>
       <c r="R106" t="n">
-        <v>2.81</v>
+        <v>1.62</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21531,10 +21531,10 @@
         <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG107" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>3.38</v>
+        <v>2.48</v>
       </c>
       <c r="Q109" t="n">
-        <v>4.22</v>
+        <v>3.13</v>
       </c>
       <c r="R109" t="n">
-        <v>2.07</v>
+        <v>2.88</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,16 +21925,16 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG109" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH109" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI109" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22325,10 +22325,10 @@
         <v>0</v>
       </c>
       <c r="AG111" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH111" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF112" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q115" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R115" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF115" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,7 +23999,7 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24043,7 +24043,7 @@
       </c>
       <c r="O120" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24787,22 +24787,22 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24835,13 +24835,13 @@
         </is>
       </c>
       <c r="P124" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q124" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R124" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S124" t="n">
         <v>0</v>
@@ -24880,10 +24880,10 @@
         <v>0</v>
       </c>
       <c r="AE124" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF124" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG124" t="n">
         <v>0</v>
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q126" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="R126" t="n">
-        <v>0</v>
+        <v>4.58</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1344,7 +1344,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1354,12 +1354,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,13 +1786,13 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.16</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,13 +2180,13 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>3.16</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="S9" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5875,7 +5875,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,13 +6514,13 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R31" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="S31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,22 +7057,22 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R35" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q36" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R36" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7741,10 +7741,10 @@
         <v>0</v>
       </c>
       <c r="AE37" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF37" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG37" t="n">
         <v>0</v>
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R39" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.77</v>
+        <v>1.54</v>
       </c>
       <c r="Q40" t="n">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="R40" t="n">
-        <v>4.09</v>
+        <v>5.37</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.76</v>
+        <v>1.86</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.96</v>
+        <v>1.84</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>2.22</v>
+        <v>1.28</v>
       </c>
       <c r="Q41" t="n">
-        <v>3.5</v>
+        <v>5.32</v>
       </c>
       <c r="R41" t="n">
-        <v>2.92</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.54</v>
+        <v>1.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="R42" t="n">
-        <v>5.37</v>
+        <v>4.09</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.86</v>
+        <v>1.76</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.84</v>
+        <v>1.96</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q48" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R48" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R50" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R52" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Portugal LigaPro</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>GD Chaves</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>União de Leiria</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.08</v>
+        <v>2.99</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.28</v>
+        <v>3.65</v>
       </c>
       <c r="R53" t="n">
-        <v>3.47</v>
+        <v>2.18</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10893,10 +10893,10 @@
         <v>0</v>
       </c>
       <c r="AE53" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="AF53" t="n">
-        <v>1.61</v>
+        <v>0</v>
       </c>
       <c r="AG53" t="n">
         <v>0</v>
@@ -10997,7 +10997,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Portugal LigaPro</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -11007,12 +11007,12 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>GD Chaves</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>União de Leiria</t>
         </is>
       </c>
       <c r="G54" t="n">
@@ -11045,13 +11045,13 @@
         </is>
       </c>
       <c r="P54" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Q54" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R54" t="n">
-        <v>0</v>
+        <v>3.47</v>
       </c>
       <c r="S54" t="n">
         <v>0</v>
@@ -11090,10 +11090,10 @@
         <v>0</v>
       </c>
       <c r="AE54" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="AF54" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AG54" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>3.55</v>
+        <v>2.14</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="R56" t="n">
-        <v>2.02</v>
+        <v>3.35</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="R57" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R58" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.85</v>
+        <v>2.28</v>
       </c>
       <c r="Q59" t="n">
-        <v>3</v>
+        <v>2.75</v>
       </c>
       <c r="R59" t="n">
-        <v>2.02</v>
+        <v>3.46</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12420,17 +12420,17 @@
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P61" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Q61" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R61" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R62" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>2.28</v>
+        <v>4</v>
       </c>
       <c r="Q63" t="n">
-        <v>2.75</v>
+        <v>3.76</v>
       </c>
       <c r="R63" t="n">
-        <v>3.46</v>
+        <v>1.77</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q64" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R64" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.32</v>
+        <v>2.45</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="R65" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.08</v>
+        <v>0</v>
       </c>
       <c r="R66" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.28</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.52</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.41</v>
+        <v>2.67</v>
       </c>
       <c r="Q70" t="n">
         <v>3.08</v>
       </c>
       <c r="R70" t="n">
-        <v>3.06</v>
+        <v>2.69</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R71" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q72" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R72" t="n">
-        <v>0</v>
+        <v>2.69</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF72" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14740,7 +14740,7 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q73" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R73" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Q74" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="R74" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.34</v>
+        <v>3.62</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="R75" t="n">
-        <v>3.21</v>
+        <v>2.03</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.93</v>
+        <v>2.34</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.74</v>
+        <v>3.05</v>
       </c>
       <c r="R76" t="n">
-        <v>2.04</v>
+        <v>3.21</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.48</v>
+        <v>2.93</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.36</v>
+        <v>3.74</v>
       </c>
       <c r="R77" t="n">
-        <v>2.69</v>
+        <v>2.04</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF77" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>3.62</v>
+        <v>2.12</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.35</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>2.03</v>
+        <v>2.98</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q80" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R80" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF80" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q82" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R82" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>2.88</v>
+        <v>1.88</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.34</v>
+        <v>3.54</v>
       </c>
       <c r="R83" t="n">
-        <v>2.25</v>
+        <v>3.5</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.92</v>
+        <v>1.82</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R86" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>3.01</v>
+        <v>2.4</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.38</v>
+        <v>3.5</v>
       </c>
       <c r="R87" t="n">
-        <v>2.42</v>
+        <v>2.65</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17591,10 +17591,10 @@
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF87" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q88" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R88" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q89" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R89" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18334,13 +18334,13 @@
         </is>
       </c>
       <c r="P91" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R91" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S91" t="n">
         <v>0</v>
@@ -18385,10 +18385,10 @@
         <v>0</v>
       </c>
       <c r="AG91" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>0</v>
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="R95" t="n">
-        <v>2.28</v>
+        <v>3.4</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF95" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.36</v>
+        <v>4.67</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.36</v>
+        <v>3.74</v>
       </c>
       <c r="R96" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF96" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>2.3</v>
+        <v>1.35</v>
       </c>
       <c r="Q97" t="n">
-        <v>3.49</v>
+        <v>5.58</v>
       </c>
       <c r="R97" t="n">
-        <v>2.81</v>
+        <v>10.4</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q98" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="R98" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,7 +19862,7 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -19872,12 +19872,12 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.35</v>
+        <v>6.01</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.58</v>
+        <v>4.1</v>
       </c>
       <c r="R99" t="n">
-        <v>10.4</v>
+        <v>1.45</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R100" t="n">
-        <v>2.87</v>
+        <v>2.28</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF100" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,7 +20256,7 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Q101" t="n">
-        <v>0</v>
+        <v>3.77</v>
       </c>
       <c r="R101" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.77</v>
+        <v>3.49</v>
       </c>
       <c r="R102" t="n">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20546,10 +20546,10 @@
         <v>0</v>
       </c>
       <c r="AE102" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF102" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG102" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>5.38</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.52</v>
+        <v>0</v>
       </c>
       <c r="R104" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>6.01</v>
+        <v>0</v>
       </c>
       <c r="Q105" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="R105" t="n">
-        <v>1.45</v>
+        <v>0</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>4.67</v>
+        <v>5.38</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.74</v>
+        <v>3.52</v>
       </c>
       <c r="R106" t="n">
-        <v>1.62</v>
+        <v>1.59</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21537,10 +21537,10 @@
         <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH107" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI107" t="n">
         <v>0</v>
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22325,10 +22325,10 @@
         <v>0</v>
       </c>
       <c r="AG111" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH111" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI111" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23062,13 +23062,13 @@
         </is>
       </c>
       <c r="P115" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q115" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R115" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S115" t="n">
         <v>0</v>
@@ -23107,10 +23107,10 @@
         <v>0</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF115" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG115" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q121" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R121" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF121" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G124" t="n">

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -1195,79 +1195,79 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.31</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AO4" t="n">
         <v>0</v>
@@ -1309,19 +1309,19 @@
         <v>0</v>
       </c>
       <c r="BB4" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC4" t="n">
-        <v>0</v>
+        <v>2.26</v>
       </c>
       <c r="BD4" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE4" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="BF4" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG4" t="n">
         <v>0</v>
@@ -1344,22 +1344,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Neftchi</t>
+          <t>Kapaz</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lokomotiv</t>
+          <t>Qarabağ</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1541,22 +1541,22 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Kapaz</t>
+          <t>Neftchi</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Qarabağ</t>
+          <t>Lokomotiv</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Wuxi Wugou</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Shenzhen Juniors</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,79 +1786,79 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>2.53</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>3.84</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>3.22</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AO7" t="n">
         <v>0</v>
@@ -1900,19 +1900,19 @@
         <v>0</v>
       </c>
       <c r="BB7" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="BC7" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="BD7" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="BE7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="BF7" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -1935,7 +1935,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Wuxi Wugou</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shenzhen Juniors</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -2189,70 +2189,70 @@
         <v>2.08</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO9" t="n">
         <v>0</v>
@@ -2261,52 +2261,52 @@
         <v>0</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR9" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS9" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU9" t="n">
         <v>0</v>
       </c>
       <c r="AV9" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW9" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX9" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY9" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="BA9" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="BB9" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC9" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD9" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE9" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BF9" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -4299,22 +4299,22 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>3.24</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4496,7 +4496,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4544,13 +4544,13 @@
         </is>
       </c>
       <c r="P21" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
         <v>0</v>
@@ -4589,10 +4589,10 @@
         <v>0</v>
       </c>
       <c r="AE21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF21" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG21" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Prostějov</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Zbrojovka Brno</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4890,7 +4890,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -4900,12 +4900,12 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Prostějov</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Zbrojovka Brno</t>
         </is>
       </c>
       <c r="G23" t="n">
@@ -5087,7 +5087,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -5097,12 +5097,12 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>4.66</v>
+        <v>2.98</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.1</v>
+        <v>2.67</v>
       </c>
       <c r="R24" t="n">
-        <v>1.56</v>
+        <v>2.79</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.98</v>
+        <v>4.66</v>
       </c>
       <c r="Q25" t="n">
-        <v>2.67</v>
+        <v>4.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.79</v>
+        <v>1.56</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>3.3</v>
+        <v>0</v>
       </c>
       <c r="R27" t="n">
-        <v>3.17</v>
+        <v>0</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,13 +6711,13 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="R32" t="n">
-        <v>5.55</v>
+        <v>0</v>
       </c>
       <c r="S32" t="n">
         <v>0</v>
@@ -6860,22 +6860,22 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,13 +7302,13 @@
         </is>
       </c>
       <c r="P35" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="Q35" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R35" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="S35" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q38" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R38" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF38" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q39" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R39" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8287,13 +8287,13 @@
         </is>
       </c>
       <c r="P40" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R40" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S40" t="n">
         <v>0</v>
@@ -8332,10 +8332,10 @@
         <v>0</v>
       </c>
       <c r="AE40" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF40" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG40" t="n">
         <v>0</v>
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8484,13 +8484,13 @@
         </is>
       </c>
       <c r="P41" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R41" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S41" t="n">
         <v>0</v>
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,22 +9224,22 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q47" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R47" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF47" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9815,22 +9815,22 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9863,13 +9863,13 @@
         </is>
       </c>
       <c r="P48" t="n">
-        <v>2.01</v>
+        <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R48" t="n">
-        <v>3.26</v>
+        <v>0</v>
       </c>
       <c r="S48" t="n">
         <v>0</v>
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="Q50" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="R50" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>1.58</v>
+        <v>2.01</v>
       </c>
       <c r="Q51" t="n">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>4.96</v>
+        <v>3.26</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10603,7 +10603,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="Q52" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="R52" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.99</v>
+        <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="R53" t="n">
-        <v>2.18</v>
+        <v>0</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R56" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>3.85</v>
+        <v>2.14</v>
       </c>
       <c r="Q57" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="R57" t="n">
-        <v>2.02</v>
+        <v>3.35</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.28</v>
+        <v>3.32</v>
       </c>
       <c r="Q59" t="n">
-        <v>2.75</v>
+        <v>3.66</v>
       </c>
       <c r="R59" t="n">
-        <v>3.46</v>
+        <v>2.05</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R60" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.2</v>
+        <v>3.76</v>
       </c>
       <c r="R61" t="n">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,22 +12573,22 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="Q62" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R62" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,13 +12818,13 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.76</v>
+        <v>3</v>
       </c>
       <c r="R63" t="n">
-        <v>1.77</v>
+        <v>2.02</v>
       </c>
       <c r="S63" t="n">
         <v>0</v>
@@ -12967,7 +12967,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.32</v>
+        <v>3.55</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="R64" t="n">
-        <v>2.05</v>
+        <v>2.02</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13164,7 +13164,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13212,13 +13212,13 @@
         </is>
       </c>
       <c r="P65" t="n">
-        <v>2.45</v>
+        <v>3.56</v>
       </c>
       <c r="Q65" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>2.75</v>
+        <v>2.1</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13257,10 +13257,10 @@
         <v>0</v>
       </c>
       <c r="AE65" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF65" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG65" t="n">
         <v>0</v>
@@ -13361,7 +13361,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>0</v>
+        <v>2.93</v>
       </c>
       <c r="Q66" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="R66" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13558,7 +13558,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -13568,12 +13568,12 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q69" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R69" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.67</v>
+        <v>2.12</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.08</v>
+        <v>3.6</v>
       </c>
       <c r="R70" t="n">
-        <v>2.69</v>
+        <v>2.98</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q71" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R71" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF71" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.36</v>
+        <v>3.34</v>
       </c>
       <c r="R72" t="n">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.83</v>
+        <v>1.92</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.95</v>
+        <v>1.76</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.7</v>
+        <v>2.41</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="R73" t="n">
-        <v>2.52</v>
+        <v>3.06</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.41</v>
+        <v>3.62</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.08</v>
+        <v>3.35</v>
       </c>
       <c r="R74" t="n">
-        <v>3.06</v>
+        <v>2.03</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>3.62</v>
+        <v>2.48</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="R75" t="n">
-        <v>2.03</v>
+        <v>2.69</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF75" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.34</v>
+        <v>2.67</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.05</v>
+        <v>3.08</v>
       </c>
       <c r="R76" t="n">
-        <v>3.21</v>
+        <v>2.69</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.93</v>
+        <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.74</v>
+        <v>0</v>
       </c>
       <c r="R77" t="n">
-        <v>2.04</v>
+        <v>0</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="R79" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Q81" t="n">
-        <v>3.34</v>
+        <v>0</v>
       </c>
       <c r="R81" t="n">
-        <v>2.25</v>
+        <v>0</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF81" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16513,7 +16513,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16561,13 +16561,13 @@
         </is>
       </c>
       <c r="P82" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q82" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R82" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S82" t="n">
         <v>0</v>
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,13 +16758,13 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="Q83" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="R83" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="S83" t="n">
         <v>0</v>
@@ -16803,10 +16803,10 @@
         <v>0</v>
       </c>
       <c r="AE83" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF83" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG83" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.02</v>
+        <v>2.46</v>
       </c>
       <c r="Q85" t="n">
-        <v>3.45</v>
+        <v>2.72</v>
       </c>
       <c r="R85" t="n">
-        <v>3.46</v>
+        <v>3.35</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17301,7 +17301,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q86" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R86" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.4</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17892,7 +17892,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -17940,13 +17940,13 @@
         </is>
       </c>
       <c r="P89" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q89" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R89" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S89" t="n">
         <v>0</v>
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q92" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R92" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,10 +18576,10 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF92" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.01</v>
+        <v>0</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="R93" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF93" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>2.36</v>
+        <v>1.35</v>
       </c>
       <c r="Q95" t="n">
-        <v>3.36</v>
+        <v>5.58</v>
       </c>
       <c r="R95" t="n">
-        <v>3.4</v>
+        <v>10.4</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>4.67</v>
+        <v>2.42</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.74</v>
+        <v>3.22</v>
       </c>
       <c r="R96" t="n">
-        <v>1.62</v>
+        <v>2.87</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19364,10 +19364,10 @@
         <v>0</v>
       </c>
       <c r="AE96" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF96" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG96" t="n">
         <v>0</v>
@@ -19468,22 +19468,22 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q97" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R97" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19665,22 +19665,22 @@
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19713,13 +19713,13 @@
         </is>
       </c>
       <c r="P98" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>3.22</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
-        <v>2.87</v>
+        <v>0</v>
       </c>
       <c r="S98" t="n">
         <v>0</v>
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>6.01</v>
+        <v>5.38</v>
       </c>
       <c r="Q99" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="R99" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,7 +20059,7 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.84</v>
+        <v>4.67</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.24</v>
+        <v>3.74</v>
       </c>
       <c r="R100" t="n">
-        <v>2.28</v>
+        <v>1.62</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AF100" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>2.1</v>
+        <v>6.01</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="R101" t="n">
-        <v>2.96</v>
+        <v>1.45</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.17</v>
+        <v>2.84</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.17</v>
+        <v>3.24</v>
       </c>
       <c r="R103" t="n">
-        <v>3.33</v>
+        <v>2.28</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF103" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q104" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="R104" t="n">
-        <v>0</v>
+        <v>3.33</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,22 +21044,22 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q105" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R105" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>5.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.52</v>
+        <v>3.77</v>
       </c>
       <c r="R106" t="n">
-        <v>1.59</v>
+        <v>2.96</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF106" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21438,22 +21438,22 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q107" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R107" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21537,10 +21537,10 @@
         <v>0</v>
       </c>
       <c r="AG107" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="n">
         <v>0</v>
@@ -21635,22 +21635,22 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q108" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R108" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21734,10 +21734,10 @@
         <v>0</v>
       </c>
       <c r="AG108" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22226,7 +22226,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -22236,12 +22236,12 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22817,7 +22817,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,7 +22861,7 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -23014,22 +23014,22 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23418,12 +23418,12 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23999,22 +23999,22 @@
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24196,22 +24196,22 @@
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24244,13 +24244,13 @@
         </is>
       </c>
       <c r="P121" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q121" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R121" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S121" t="n">
         <v>0</v>
@@ -24289,10 +24289,10 @@
         <v>0</v>
       </c>
       <c r="AE121" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF121" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG121" t="n">
         <v>0</v>
@@ -24393,7 +24393,7 @@
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24437,7 +24437,7 @@
       </c>
       <c r="O122" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="Q126" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="R126" t="n">
-        <v>4.58</v>
+        <v>5.38</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25378,22 +25378,22 @@
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,13 +25426,13 @@
         </is>
       </c>
       <c r="P127" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="Q127" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="R127" t="n">
-        <v>5.38</v>
+        <v>4.58</v>
       </c>
       <c r="S127" t="n">
         <v>0</v>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BI127"/>
+  <dimension ref="A1:BI129"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -998,133 +998,133 @@
         </is>
       </c>
       <c r="P3" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="Q3" t="n">
-        <v>4.12</v>
+        <v>4.2</v>
       </c>
       <c r="R3" t="n">
-        <v>3.42</v>
+        <v>3.6</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO3" t="n">
         <v>0</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR3" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AS3" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AT3" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AU3" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AV3" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW3" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="AX3" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AY3" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BA3" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BB3" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC3" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="BD3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="BF3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG3" t="n">
         <v>0</v>
@@ -1195,13 +1195,13 @@
         </is>
       </c>
       <c r="P4" t="n">
-        <v>2.5</v>
+        <v>2.64</v>
       </c>
       <c r="Q4" t="n">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7</v>
+        <v>2.95</v>
       </c>
       <c r="S4" t="n">
         <v>3.34</v>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>China Chinese Super League</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1748,12 +1748,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Atyrau</t>
+          <t>Dalian Zhixing</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Zhenys</t>
+          <t>Shanghai SIPG</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1786,133 +1786,133 @@
         </is>
       </c>
       <c r="P7" t="n">
-        <v>3.06</v>
+        <v>3.16</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.91</v>
+        <v>4</v>
       </c>
       <c r="R7" t="n">
-        <v>2.53</v>
+        <v>2.08</v>
       </c>
       <c r="S7" t="n">
-        <v>3.84</v>
+        <v>3.22</v>
       </c>
       <c r="T7" t="n">
-        <v>1.83</v>
+        <v>2.35</v>
       </c>
       <c r="U7" t="n">
-        <v>3.22</v>
+        <v>2.24</v>
       </c>
       <c r="V7" t="n">
-        <v>1.49</v>
+        <v>1.21</v>
       </c>
       <c r="W7" t="n">
-        <v>2.36</v>
+        <v>3.68</v>
       </c>
       <c r="X7" t="n">
-        <v>3.08</v>
+        <v>2.17</v>
       </c>
       <c r="Y7" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>4.55</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>4.95</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>2.43</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AJ7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AK7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AL7" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AM7" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AO7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AS7" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AT7" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="AU7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AZ7" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="BA7" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="BB7" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="BC7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="BF7" t="n">
         <v>1.3</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>8.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AE7" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AF7" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="AG7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.03</v>
-      </c>
-      <c r="AK7" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AL7" t="n">
-        <v>1.89</v>
-      </c>
-      <c r="AM7" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>1.34</v>
-      </c>
-      <c r="AO7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA7" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB7" t="n">
-        <v>1.24</v>
-      </c>
-      <c r="BC7" t="n">
-        <v>2.22</v>
-      </c>
-      <c r="BD7" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="BE7" t="n">
-        <v>1.58</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>1.11</v>
       </c>
       <c r="BG7" t="n">
         <v>0</v>
@@ -2132,7 +2132,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>China Chinese Super League</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -2142,12 +2142,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Dalian Zhixing</t>
+          <t>Atyrau</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Shanghai SIPG</t>
+          <t>Zhenys</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -2180,133 +2180,133 @@
         </is>
       </c>
       <c r="P9" t="n">
-        <v>3.16</v>
+        <v>3.05</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R9" t="n">
-        <v>2.08</v>
+        <v>2.38</v>
       </c>
       <c r="S9" t="n">
-        <v>3.4</v>
+        <v>3.84</v>
       </c>
       <c r="T9" t="n">
-        <v>2.4</v>
+        <v>1.82</v>
       </c>
       <c r="U9" t="n">
-        <v>2.45</v>
+        <v>3.25</v>
       </c>
       <c r="V9" t="n">
-        <v>1.22</v>
+        <v>1.5</v>
       </c>
       <c r="W9" t="n">
-        <v>3.6</v>
+        <v>2.33</v>
       </c>
       <c r="X9" t="n">
-        <v>2.23</v>
+        <v>3.08</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.6</v>
+        <v>1.3</v>
       </c>
       <c r="Z9" t="n">
-        <v>4.75</v>
+        <v>8.5</v>
       </c>
       <c r="AA9" t="n">
-        <v>1.13</v>
+        <v>1.01</v>
       </c>
       <c r="AB9" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AC9" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AD9" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AE9" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AF9" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="AG9" t="n">
+        <v>3.58</v>
+      </c>
+      <c r="AH9" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="AJ9" t="n">
         <v>1.03</v>
       </c>
-      <c r="AC9" t="n">
-        <v>1.15</v>
-      </c>
-      <c r="AD9" t="n">
-        <v>5</v>
-      </c>
-      <c r="AE9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AF9" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="AH9" t="n">
+      <c r="AK9" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AL9" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AM9" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AO9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA9" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB9" t="n">
+        <v>1.24</v>
+      </c>
+      <c r="BC9" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>3.34</v>
+      </c>
+      <c r="BE9" t="n">
         <v>1.57</v>
       </c>
-      <c r="AI9" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AJ9" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AK9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AL9" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="AM9" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AO9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ9" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="AS9" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AT9" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="AU9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV9" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="AW9" t="n">
-        <v>2.23</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>1.98</v>
-      </c>
-      <c r="BA9" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="BB9" t="n">
-        <v>1.17</v>
-      </c>
-      <c r="BC9" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="BD9" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="BE9" t="n">
-        <v>2</v>
-      </c>
       <c r="BF9" t="n">
-        <v>1.29</v>
+        <v>1.1</v>
       </c>
       <c r="BG9" t="n">
         <v>0</v>
@@ -2583,124 +2583,124 @@
         <v>2.18</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AO11" t="n">
         <v>0</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS11" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT11" t="n">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="AU11" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AV11" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW11" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX11" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY11" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="BA11" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BB11" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC11" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="BD11" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE11" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BF11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG11" t="n">
         <v>0</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>China China League One</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Guangxi Hengchen</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Termez Surkhon</t>
+          <t>Shanghai Jiading</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -2920,7 +2920,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>China China League One</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2930,12 +2930,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Guangxi Hengchen</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Shanghai Jiading</t>
+          <t>Termez Surkhon</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -3165,79 +3165,79 @@
         </is>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>5.25</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>3.14</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO14" t="n">
         <v>0</v>
@@ -3279,19 +3279,19 @@
         <v>0</v>
       </c>
       <c r="BB14" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="BC14" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="BD14" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="BE14" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BF14" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BG14" t="n">
         <v>0</v>
@@ -3506,12 +3506,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>India Indian Super League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>ATK Mohun Bagan</t>
+          <t>Rabotnički</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Mumbai City</t>
+          <t>Sileks</t>
         </is>
       </c>
       <c r="G16" t="n">
@@ -3559,13 +3559,13 @@
         </is>
       </c>
       <c r="P16" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>4.04</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>5.29</v>
+        <v>0</v>
       </c>
       <c r="S16" t="n">
         <v>0</v>
@@ -3694,7 +3694,7 @@
         <v>0</v>
       </c>
       <c r="BI16" s="3" t="n">
-        <v>46101.45833333334</v>
+        <v>46101.4375</v>
       </c>
     </row>
     <row r="17">
@@ -3703,27 +3703,27 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>11:00</t>
+          <t>10:30</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Kazakhstan Kazakhstan Premier League</t>
+          <t>FYR Macedonia First Football League</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Astana</t>
+          <t>Tikveš</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tobol</t>
+          <t>Akademija Pandev</t>
         </is>
       </c>
       <c r="G17" t="n">
@@ -3891,7 +3891,7 @@
         <v>0</v>
       </c>
       <c r="BI17" s="3" t="n">
-        <v>46101.45833333334</v>
+        <v>46101.4375</v>
       </c>
     </row>
     <row r="18">
@@ -3900,12 +3900,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>India Indian Super League</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -3915,12 +3915,12 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Haras El Hodood</t>
+          <t>ATK Mohun Bagan</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ismaily SC</t>
+          <t>Mumbai City</t>
         </is>
       </c>
       <c r="G18" t="n">
@@ -3953,79 +3953,79 @@
         </is>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>4.04</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>5.29</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>5.9</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AO18" t="n">
         <v>0</v>
@@ -4067,19 +4067,19 @@
         <v>0</v>
       </c>
       <c r="BB18" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC18" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="BD18" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE18" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BF18" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG18" t="n">
         <v>0</v>
@@ -4088,7 +4088,7 @@
         <v>0</v>
       </c>
       <c r="BI18" s="3" t="n">
-        <v>46101.5</v>
+        <v>46101.45833333334</v>
       </c>
     </row>
     <row r="19">
@@ -4097,27 +4097,27 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>11:00</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Azerbaijan Premyer Liqası</t>
+          <t>Kazakhstan Kazakhstan Premier League</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Neftçi</t>
+          <t>Astana</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Mil Mugan FK</t>
+          <t>Tobol</t>
         </is>
       </c>
       <c r="G19" t="n">
@@ -4150,79 +4150,79 @@
         </is>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>4.96</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>6.3</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>2.97</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>5.45</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="AO19" t="n">
         <v>0</v>
@@ -4264,19 +4264,19 @@
         <v>0</v>
       </c>
       <c r="BB19" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BC19" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BD19" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="BE19" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="BF19" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="BG19" t="n">
         <v>0</v>
@@ -4285,7 +4285,7 @@
         <v>0</v>
       </c>
       <c r="BI19" s="3" t="n">
-        <v>46101.51041666666</v>
+        <v>46101.45833333334</v>
       </c>
     </row>
     <row r="20">
@@ -4294,12 +4294,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:00</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -4309,12 +4309,12 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Haras El Hodood</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Ismaily SC</t>
         </is>
       </c>
       <c r="G20" t="n">
@@ -4347,13 +4347,13 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>2.83</v>
+        <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>3.24</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>2.43</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
         <v>0</v>
@@ -4392,10 +4392,10 @@
         <v>0</v>
       </c>
       <c r="AE20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AF20" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="n">
         <v>0</v>
@@ -4482,7 +4482,7 @@
         <v>0</v>
       </c>
       <c r="BI20" s="3" t="n">
-        <v>46101.54166666666</v>
+        <v>46101.5</v>
       </c>
     </row>
     <row r="21">
@@ -4491,12 +4491,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>12:15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Azerbaijan Premyer Liqası</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -4506,12 +4506,12 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Neftçi</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Mil Mugan FK</t>
         </is>
       </c>
       <c r="G21" t="n">
@@ -4679,7 +4679,7 @@
         <v>0</v>
       </c>
       <c r="BI21" s="3" t="n">
-        <v>46101.54166666666</v>
+        <v>46101.51041666666</v>
       </c>
     </row>
     <row r="22">
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -4938,13 +4938,13 @@
         </is>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="S23" t="n">
         <v>0</v>
@@ -5082,27 +5082,27 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,13 +5135,13 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>2.98</v>
+        <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>2.67</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.79</v>
+        <v>0</v>
       </c>
       <c r="S24" t="n">
         <v>0</v>
@@ -5270,7 +5270,7 @@
         <v>0</v>
       </c>
       <c r="BI24" s="3" t="n">
-        <v>46101.5625</v>
+        <v>46101.54166666666</v>
       </c>
     </row>
     <row r="25">
@@ -5279,12 +5279,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,13 +5332,13 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>4.66</v>
+        <v>2.83</v>
       </c>
       <c r="Q25" t="n">
-        <v>4.1</v>
+        <v>3.24</v>
       </c>
       <c r="R25" t="n">
-        <v>1.56</v>
+        <v>2.43</v>
       </c>
       <c r="S25" t="n">
         <v>0</v>
@@ -5377,10 +5377,10 @@
         <v>0</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG25" t="n">
         <v>0</v>
@@ -5467,7 +5467,7 @@
         <v>0</v>
       </c>
       <c r="BI25" s="3" t="n">
-        <v>46101.5625</v>
+        <v>46101.54166666666</v>
       </c>
     </row>
     <row r="26">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,13 +5529,13 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>1.63</v>
+        <v>4.66</v>
       </c>
       <c r="Q26" t="n">
-        <v>3.55</v>
+        <v>4.1</v>
       </c>
       <c r="R26" t="n">
-        <v>5.55</v>
+        <v>1.56</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>0</v>
       </c>
       <c r="BI26" s="3" t="n">
-        <v>46101.58333333334</v>
+        <v>46101.5625</v>
       </c>
     </row>
     <row r="27">
@@ -5673,12 +5673,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>14:00</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,13 +5726,13 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>2.79</v>
       </c>
       <c r="S27" t="n">
         <v>0</v>
@@ -5861,7 +5861,7 @@
         <v>0</v>
       </c>
       <c r="BI27" s="3" t="n">
-        <v>46101.58333333334</v>
+        <v>46101.5625</v>
       </c>
     </row>
     <row r="28">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6466,22 +6466,22 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6663,22 +6663,22 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,13 +6908,13 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>5.55</v>
       </c>
       <c r="S33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>2.81</v>
+        <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="R34" t="n">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF34" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7499,13 +7499,13 @@
         </is>
       </c>
       <c r="P36" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R36" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S36" t="n">
         <v>0</v>
@@ -7648,22 +7648,22 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q37" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R37" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -7893,13 +7893,13 @@
         </is>
       </c>
       <c r="P38" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R38" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S38" t="n">
         <v>0</v>
@@ -7938,10 +7938,10 @@
         <v>0</v>
       </c>
       <c r="AE38" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF38" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG38" t="n">
         <v>0</v>
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>1.28</v>
+        <v>2.81</v>
       </c>
       <c r="Q39" t="n">
-        <v>5.32</v>
+        <v>3.46</v>
       </c>
       <c r="R39" t="n">
-        <v>8.369999999999999</v>
+        <v>2.32</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AF39" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q42" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R42" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AF42" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q43" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R43" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q44" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R44" t="n">
-        <v>0</v>
+        <v>5.37</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AF44" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9618,22 +9618,22 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9666,13 +9666,13 @@
         </is>
       </c>
       <c r="P47" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R47" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S47" t="n">
         <v>0</v>
@@ -9711,10 +9711,10 @@
         <v>0</v>
       </c>
       <c r="AE47" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF47" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG47" t="n">
         <v>0</v>
@@ -9810,27 +9810,27 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Lithuania A Lyga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Trakai</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>FA Šiauliai</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -9998,7 +9998,7 @@
         <v>0</v>
       </c>
       <c r="BI48" s="3" t="n">
-        <v>46101.60416666666</v>
+        <v>46101.58333333334</v>
       </c>
     </row>
     <row r="49">
@@ -10007,12 +10007,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>14:00</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -10022,12 +10022,12 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10060,13 +10060,13 @@
         </is>
       </c>
       <c r="P49" t="n">
-        <v>5.88</v>
+        <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>3.75</v>
+        <v>0</v>
       </c>
       <c r="R49" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="S49" t="n">
         <v>0</v>
@@ -10195,7 +10195,7 @@
         <v>0</v>
       </c>
       <c r="BI49" s="3" t="n">
-        <v>46101.60416666666</v>
+        <v>46101.58333333334</v>
       </c>
     </row>
     <row r="50">
@@ -10209,22 +10209,22 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Lithuania A Lyga</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Hannover 96</t>
+          <t>Trakai</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Eintracht Braunschweig</t>
+          <t>FA Šiauliai</t>
         </is>
       </c>
       <c r="G50" t="n">
@@ -10257,13 +10257,13 @@
         </is>
       </c>
       <c r="P50" t="n">
-        <v>1.58</v>
+        <v>2.84</v>
       </c>
       <c r="Q50" t="n">
-        <v>4.1</v>
+        <v>3.45</v>
       </c>
       <c r="R50" t="n">
-        <v>4.96</v>
+        <v>2.22</v>
       </c>
       <c r="S50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>2.01</v>
+        <v>5.88</v>
       </c>
       <c r="Q51" t="n">
         <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>3.26</v>
+        <v>1.73</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10598,12 +10598,12 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -10613,12 +10613,12 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Hannover 96</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Eintracht Braunschweig</t>
         </is>
       </c>
       <c r="G52" t="n">
@@ -10651,13 +10651,13 @@
         </is>
       </c>
       <c r="P52" t="n">
-        <v>2.99</v>
+        <v>1.58</v>
       </c>
       <c r="Q52" t="n">
-        <v>3.65</v>
+        <v>4.1</v>
       </c>
       <c r="R52" t="n">
-        <v>2.18</v>
+        <v>4.96</v>
       </c>
       <c r="S52" t="n">
         <v>0</v>
@@ -10786,7 +10786,7 @@
         <v>0</v>
       </c>
       <c r="BI52" s="3" t="n">
-        <v>46101.625</v>
+        <v>46101.60416666666</v>
       </c>
     </row>
     <row r="53">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>14:30</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,13 +10848,13 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>0</v>
+        <v>2.01</v>
       </c>
       <c r="Q53" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R53" t="n">
-        <v>0</v>
+        <v>3.26</v>
       </c>
       <c r="S53" t="n">
         <v>0</v>
@@ -10983,7 +10983,7 @@
         <v>0</v>
       </c>
       <c r="BI53" s="3" t="n">
-        <v>46101.625</v>
+        <v>46101.60416666666</v>
       </c>
     </row>
     <row r="54">
@@ -11386,12 +11386,12 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,13 +11439,13 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.28</v>
+        <v>2.99</v>
       </c>
       <c r="Q56" t="n">
-        <v>2.75</v>
+        <v>3.65</v>
       </c>
       <c r="R56" t="n">
-        <v>3.46</v>
+        <v>2.18</v>
       </c>
       <c r="S56" t="n">
         <v>0</v>
@@ -11574,7 +11574,7 @@
         <v>0</v>
       </c>
       <c r="BI56" s="3" t="n">
-        <v>46101.64583333334</v>
+        <v>46101.625</v>
       </c>
     </row>
     <row r="57">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,13 +11636,13 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R57" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S57" t="n">
         <v>0</v>
@@ -11771,7 +11771,7 @@
         <v>0</v>
       </c>
       <c r="BI57" s="3" t="n">
-        <v>46101.64583333334</v>
+        <v>46101.625</v>
       </c>
     </row>
     <row r="58">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11829,17 +11829,17 @@
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P58" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="Q58" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R58" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12030,13 +12030,13 @@
         </is>
       </c>
       <c r="P59" t="n">
-        <v>3.32</v>
+        <v>2.45</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.66</v>
+        <v>3.2</v>
       </c>
       <c r="R59" t="n">
-        <v>2.05</v>
+        <v>2.75</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AF59" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,22 +12179,22 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,13 +12227,13 @@
         </is>
       </c>
       <c r="P60" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Q60" t="n">
-        <v>0</v>
+        <v>3.66</v>
       </c>
       <c r="R60" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="S60" t="n">
         <v>0</v>
@@ -12376,7 +12376,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,13 +12424,13 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>4</v>
+        <v>2.14</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.76</v>
+        <v>3.1</v>
       </c>
       <c r="R61" t="n">
-        <v>1.77</v>
+        <v>3.35</v>
       </c>
       <c r="S61" t="n">
         <v>0</v>
@@ -12573,7 +12573,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,13 +12621,13 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>2.45</v>
+        <v>3.85</v>
       </c>
       <c r="Q62" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R62" t="n">
-        <v>2.75</v>
+        <v>2.02</v>
       </c>
       <c r="S62" t="n">
         <v>0</v>
@@ -12666,10 +12666,10 @@
         <v>0</v>
       </c>
       <c r="AE62" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF62" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG62" t="n">
         <v>0</v>
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,10 +12818,10 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="Q63" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R63" t="n">
         <v>2.02</v>
@@ -12977,12 +12977,12 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.55</v>
+        <v>3.56</v>
       </c>
       <c r="Q64" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="R64" t="n">
-        <v>2.02</v>
+        <v>2.1</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,17 +13208,17 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R65" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S65" t="n">
         <v>0</v>
@@ -13356,12 +13356,12 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,13 +13409,13 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>2.93</v>
+        <v>4</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.74</v>
+        <v>3.76</v>
       </c>
       <c r="R66" t="n">
-        <v>2.04</v>
+        <v>1.77</v>
       </c>
       <c r="S66" t="n">
         <v>0</v>
@@ -13544,7 +13544,7 @@
         <v>0</v>
       </c>
       <c r="BI66" s="3" t="n">
-        <v>46101.66666666666</v>
+        <v>46101.64583333334</v>
       </c>
     </row>
     <row r="67">
@@ -13553,27 +13553,27 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,13 +13606,13 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>2.36</v>
+        <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="R67" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S67" t="n">
         <v>0</v>
@@ -13741,7 +13741,7 @@
         <v>0</v>
       </c>
       <c r="BI67" s="3" t="n">
-        <v>46101.66666666666</v>
+        <v>46101.64583333334</v>
       </c>
     </row>
     <row r="68">
@@ -13755,7 +13755,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,13 +13803,13 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="R68" t="n">
-        <v>3.21</v>
+        <v>0</v>
       </c>
       <c r="S68" t="n">
         <v>0</v>
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>2.7</v>
+        <v>3.62</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.28</v>
+        <v>3.35</v>
       </c>
       <c r="R69" t="n">
-        <v>2.52</v>
+        <v>2.03</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14149,7 +14149,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.12</v>
+        <v>2.34</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.6</v>
+        <v>3.05</v>
       </c>
       <c r="R70" t="n">
-        <v>2.98</v>
+        <v>3.21</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14346,7 +14346,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>1.88</v>
+        <v>2.41</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.54</v>
+        <v>3.08</v>
       </c>
       <c r="R71" t="n">
-        <v>3.5</v>
+        <v>3.06</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14439,10 +14439,10 @@
         <v>0</v>
       </c>
       <c r="AE71" t="n">
-        <v>1.82</v>
+        <v>0</v>
       </c>
       <c r="AF71" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AG71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.88</v>
+        <v>2.93</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.34</v>
+        <v>3.74</v>
       </c>
       <c r="R72" t="n">
-        <v>2.25</v>
+        <v>2.04</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14636,10 +14636,10 @@
         <v>0</v>
       </c>
       <c r="AE72" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AF72" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AG72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.41</v>
+        <v>2.7</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.08</v>
+        <v>3.28</v>
       </c>
       <c r="R73" t="n">
-        <v>3.06</v>
+        <v>2.52</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>3.62</v>
+        <v>2.48</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="R74" t="n">
-        <v>2.03</v>
+        <v>2.69</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF74" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15134,7 +15134,7 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15182,13 +15182,13 @@
         </is>
       </c>
       <c r="P75" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>3.36</v>
+        <v>0</v>
       </c>
       <c r="R75" t="n">
-        <v>2.69</v>
+        <v>0</v>
       </c>
       <c r="S75" t="n">
         <v>0</v>
@@ -15227,10 +15227,10 @@
         <v>0</v>
       </c>
       <c r="AE75" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF75" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG75" t="n">
         <v>0</v>
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,13 +15379,13 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.67</v>
+        <v>2.88</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.08</v>
+        <v>3.34</v>
       </c>
       <c r="R76" t="n">
-        <v>2.69</v>
+        <v>2.25</v>
       </c>
       <c r="S76" t="n">
         <v>0</v>
@@ -15424,10 +15424,10 @@
         <v>0</v>
       </c>
       <c r="AE76" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF76" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="Q77" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="R77" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,13 +15773,13 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q78" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R78" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S78" t="n">
         <v>0</v>
@@ -15818,10 +15818,10 @@
         <v>0</v>
       </c>
       <c r="AE78" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF78" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q79" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="R79" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16902,12 +16902,12 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Vaduz</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Yverdon Sport</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,13 +16955,13 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>1.92</v>
+        <v>2.67</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.7</v>
+        <v>3.08</v>
       </c>
       <c r="R84" t="n">
-        <v>3.51</v>
+        <v>2.69</v>
       </c>
       <c r="S84" t="n">
         <v>0</v>
@@ -17090,7 +17090,7 @@
         <v>0</v>
       </c>
       <c r="BI84" s="3" t="n">
-        <v>46101.67708333334</v>
+        <v>46101.66666666666</v>
       </c>
     </row>
     <row r="85">
@@ -17099,12 +17099,12 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q85" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R85" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17287,7 +17287,7 @@
         <v>0</v>
       </c>
       <c r="BI85" s="3" t="n">
-        <v>46101.6875</v>
+        <v>46101.66666666666</v>
       </c>
     </row>
     <row r="86">
@@ -17296,12 +17296,12 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>16:30</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -17311,12 +17311,12 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Vaduz</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Yverdon Sport</t>
         </is>
       </c>
       <c r="G86" t="n">
@@ -17349,13 +17349,13 @@
         </is>
       </c>
       <c r="P86" t="n">
-        <v>2.4</v>
+        <v>1.92</v>
       </c>
       <c r="Q86" t="n">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="R86" t="n">
-        <v>2.65</v>
+        <v>3.51</v>
       </c>
       <c r="S86" t="n">
         <v>0</v>
@@ -17484,7 +17484,7 @@
         <v>0</v>
       </c>
       <c r="BI86" s="3" t="n">
-        <v>46101.6875</v>
+        <v>46101.67708333334</v>
       </c>
     </row>
     <row r="87">
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="Q87" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R87" t="n">
-        <v>0</v>
+        <v>3.46</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q88" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R88" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q90" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R90" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>3.01</v>
+        <v>1.96</v>
       </c>
       <c r="Q92" t="n">
-        <v>3.38</v>
+        <v>4.16</v>
       </c>
       <c r="R92" t="n">
-        <v>2.42</v>
+        <v>3.78</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18576,16 +18576,16 @@
         <v>0</v>
       </c>
       <c r="AE92" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH92" t="n">
         <v>1.73</v>
-      </c>
-      <c r="AG92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH92" t="n">
-        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,13 +18728,13 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q93" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R93" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S93" t="n">
         <v>0</v>
@@ -18773,10 +18773,10 @@
         <v>0</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF93" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,13 +18925,13 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q94" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R94" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S94" t="n">
         <v>0</v>
@@ -18976,10 +18976,10 @@
         <v>0</v>
       </c>
       <c r="AG94" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI94" t="n">
         <v>0</v>
@@ -19069,12 +19069,12 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q95" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R95" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19257,7 +19257,7 @@
         <v>0</v>
       </c>
       <c r="BI95" s="3" t="n">
-        <v>46101.69791666666</v>
+        <v>46101.6875</v>
       </c>
     </row>
     <row r="96">
@@ -19266,12 +19266,12 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>16:45</t>
+          <t>16:30</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.42</v>
+        <v>2.46</v>
       </c>
       <c r="Q96" t="n">
-        <v>3.22</v>
+        <v>2.72</v>
       </c>
       <c r="R96" t="n">
-        <v>2.87</v>
+        <v>3.35</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19454,7 +19454,7 @@
         <v>0</v>
       </c>
       <c r="BI96" s="3" t="n">
-        <v>46101.69791666666</v>
+        <v>46101.6875</v>
       </c>
     </row>
     <row r="97">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>5.38</v>
+        <v>1.35</v>
       </c>
       <c r="Q99" t="n">
-        <v>3.52</v>
+        <v>5.58</v>
       </c>
       <c r="R99" t="n">
-        <v>1.59</v>
+        <v>10.4</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20059,22 +20059,22 @@
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Carrick Rangers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Linfield</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>4.67</v>
+        <v>2.3</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.74</v>
+        <v>3.49</v>
       </c>
       <c r="R100" t="n">
-        <v>1.62</v>
+        <v>2.81</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20152,10 +20152,10 @@
         <v>0</v>
       </c>
       <c r="AE100" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF100" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG100" t="n">
         <v>0</v>
@@ -20256,22 +20256,22 @@
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>6.01</v>
+        <v>5.38</v>
       </c>
       <c r="Q101" t="n">
-        <v>4.1</v>
+        <v>3.52</v>
       </c>
       <c r="R101" t="n">
-        <v>1.45</v>
+        <v>1.59</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20463,12 +20463,12 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.49</v>
+        <v>3.17</v>
       </c>
       <c r="R102" t="n">
-        <v>2.81</v>
+        <v>3.33</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20650,22 +20650,22 @@
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.84</v>
+        <v>2.1</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.24</v>
+        <v>3.77</v>
       </c>
       <c r="R103" t="n">
-        <v>2.28</v>
+        <v>2.96</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.93</v>
+        <v>1.79</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.83</v>
+        <v>1.97</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,22 +20847,22 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.17</v>
+        <v>2.42</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.17</v>
+        <v>3.22</v>
       </c>
       <c r="R104" t="n">
-        <v>3.33</v>
+        <v>2.87</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -21044,7 +21044,7 @@
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -21054,12 +21054,12 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Carrick Rangers</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Linfield</t>
         </is>
       </c>
       <c r="G105" t="n">
@@ -21092,13 +21092,13 @@
         </is>
       </c>
       <c r="P105" t="n">
-        <v>2.36</v>
+        <v>4.67</v>
       </c>
       <c r="Q105" t="n">
-        <v>3.36</v>
+        <v>3.74</v>
       </c>
       <c r="R105" t="n">
-        <v>3.4</v>
+        <v>1.62</v>
       </c>
       <c r="S105" t="n">
         <v>0</v>
@@ -21137,10 +21137,10 @@
         <v>0</v>
       </c>
       <c r="AE105" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF105" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG105" t="n">
         <v>0</v>
@@ -21241,22 +21241,22 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>2.1</v>
+        <v>6.01</v>
       </c>
       <c r="Q106" t="n">
-        <v>3.77</v>
+        <v>4.1</v>
       </c>
       <c r="R106" t="n">
-        <v>2.96</v>
+        <v>1.45</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21334,10 +21334,10 @@
         <v>0</v>
       </c>
       <c r="AE106" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF106" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG106" t="n">
         <v>0</v>
@@ -21433,27 +21433,27 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="Q107" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="R107" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21621,7 +21621,7 @@
         <v>0</v>
       </c>
       <c r="BI107" s="3" t="n">
-        <v>46101.70833333334</v>
+        <v>46101.69791666666</v>
       </c>
     </row>
     <row r="108">
@@ -21630,12 +21630,12 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>17:00</t>
+          <t>16:45</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>3.38</v>
+        <v>2.84</v>
       </c>
       <c r="Q108" t="n">
-        <v>4.22</v>
+        <v>3.24</v>
       </c>
       <c r="R108" t="n">
-        <v>2.07</v>
+        <v>2.28</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,16 +21728,16 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF108" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG108" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI108" t="n">
         <v>0</v>
@@ -21818,7 +21818,7 @@
         <v>0</v>
       </c>
       <c r="BI108" s="3" t="n">
-        <v>46101.70833333334</v>
+        <v>46101.69791666666</v>
       </c>
     </row>
     <row r="109">
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q109" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R109" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF109" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R111" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF111" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22418,12 +22418,12 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>17:15</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Portugal Liga NOS</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Estrela Amadora</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Casa Pia</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>2.42</v>
+        <v>0</v>
       </c>
       <c r="Q112" t="n">
-        <v>3.39</v>
+        <v>0</v>
       </c>
       <c r="R112" t="n">
-        <v>3.09</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22516,10 +22516,10 @@
         <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
         <v>0</v>
@@ -22606,7 +22606,7 @@
         <v>0</v>
       </c>
       <c r="BI112" s="3" t="n">
-        <v>46101.71875</v>
+        <v>46101.70833333334</v>
       </c>
     </row>
     <row r="113">
@@ -22615,27 +22615,27 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>20:30</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Chile Primera B</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Unión Española</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Puerto Montt</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q113" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH113" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -22803,7 +22803,7 @@
         <v>0</v>
       </c>
       <c r="BI113" s="3" t="n">
-        <v>46101.85416666666</v>
+        <v>46101.70833333334</v>
       </c>
     </row>
     <row r="114">
@@ -22812,12 +22812,12 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>17:15</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Portugal Liga NOS</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -22827,12 +22827,12 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Estrela Amadora</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Casa Pia</t>
         </is>
       </c>
       <c r="G114" t="n">
@@ -22861,17 +22861,17 @@
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P114" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q114" t="n">
-        <v>0</v>
+        <v>3.39</v>
       </c>
       <c r="R114" t="n">
-        <v>0</v>
+        <v>3.09</v>
       </c>
       <c r="S114" t="n">
         <v>0</v>
@@ -22910,10 +22910,10 @@
         <v>0</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF114" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AG114" t="n">
         <v>0</v>
@@ -23000,7 +23000,7 @@
         <v>0</v>
       </c>
       <c r="BI114" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.71875</v>
       </c>
     </row>
     <row r="115">
@@ -23009,12 +23009,12 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>21:00</t>
+          <t>20:30</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Chile Primera B</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -23024,12 +23024,12 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Unión Española</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Puerto Montt</t>
         </is>
       </c>
       <c r="G115" t="n">
@@ -23197,7 +23197,7 @@
         <v>0</v>
       </c>
       <c r="BI115" s="3" t="n">
-        <v>46101.875</v>
+        <v>46101.85416666666</v>
       </c>
     </row>
     <row r="116">
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q116" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R116" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24600,12 +24600,12 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24979,27 +24979,27 @@
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>21:30</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Argentina Prim B Nacional</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>San Martín San Juan</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>San Martín Tucumán</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25167,7 +25167,7 @@
         <v>0</v>
       </c>
       <c r="BI125" s="3" t="n">
-        <v>46101.89583333334</v>
+        <v>46101.875</v>
       </c>
     </row>
     <row r="126">
@@ -25176,27 +25176,27 @@
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>1.6</v>
+        <v>3.54</v>
       </c>
       <c r="Q126" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="R126" t="n">
-        <v>5.38</v>
+        <v>1.95</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF126" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25364,7 +25364,7 @@
         <v>0</v>
       </c>
       <c r="BI126" s="3" t="n">
-        <v>46101.95833333334</v>
+        <v>46101.875</v>
       </c>
     </row>
     <row r="127">
@@ -25373,12 +25373,12 @@
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>23:00</t>
+          <t>21:30</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Argentina Prim B Nacional</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -25388,12 +25388,12 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>San Martín San Juan</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>San Martín Tucumán</t>
         </is>
       </c>
       <c r="G127" t="n">
@@ -25426,141 +25426,535 @@
         </is>
       </c>
       <c r="P127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI127" s="3" t="n">
+        <v>46101.89583333334</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Australia A-League</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Auckland</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>Macarthur</t>
+        </is>
+      </c>
+      <c r="G128" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0</v>
+      </c>
+      <c r="M128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N128" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O128" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P128" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="R128" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI128" s="3" t="n">
+        <v>46101.95833333334</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>23:00</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>USA NWSL</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Portland Thorns</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Seattle Reign</t>
+        </is>
+      </c>
+      <c r="G129" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0</v>
+      </c>
+      <c r="M129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="N129" t="n">
+        <v>-1</v>
+      </c>
+      <c r="O129" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="P129" t="n">
         <v>1.94</v>
       </c>
-      <c r="Q127" t="n">
+      <c r="Q129" t="n">
         <v>2.8</v>
       </c>
-      <c r="R127" t="n">
+      <c r="R129" t="n">
         <v>4.58</v>
       </c>
-      <c r="S127" t="n">
-        <v>0</v>
-      </c>
-      <c r="T127" t="n">
-        <v>0</v>
-      </c>
-      <c r="U127" t="n">
-        <v>0</v>
-      </c>
-      <c r="V127" t="n">
-        <v>0</v>
-      </c>
-      <c r="W127" t="n">
-        <v>0</v>
-      </c>
-      <c r="X127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y127" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY127" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BE127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BF127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BG127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BH127" t="n">
-        <v>0</v>
-      </c>
-      <c r="BI127" s="3" t="n">
+      <c r="S129" t="n">
+        <v>0</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0</v>
+      </c>
+      <c r="BI129" s="3" t="n">
         <v>46101.95833333334</v>
       </c>
     </row>

--- a/jogos_2026-03-20.xlsx
+++ b/jogos_2026-03-20.xlsx
@@ -4347,133 +4347,133 @@
         </is>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO20" t="n">
         <v>0</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AQ20" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AR20" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="AS20" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AT20" t="n">
         <v>0</v>
       </c>
       <c r="AU20" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AV20" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AW20" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AX20" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AY20" t="n">
         <v>0</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BA20" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BB20" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BC20" t="n">
-        <v>0</v>
+        <v>2.96</v>
       </c>
       <c r="BD20" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BE20" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BF20" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="BG20" t="n">
         <v>0</v>
@@ -4693,22 +4693,22 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Serbia SuperLiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Spartak Subotica</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Radnik Surdulica</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G22" t="n">
@@ -4741,13 +4741,13 @@
         </is>
       </c>
       <c r="P22" t="n">
-        <v>2.95</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>2.28</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
         <v>0</v>
@@ -5087,22 +5087,22 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Bulgaria First League</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Slavia Sofia</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Botev Plovdiv</t>
         </is>
       </c>
       <c r="G24" t="n">
@@ -5135,133 +5135,133 @@
         </is>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>2.99</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AO24" t="n">
         <v>0</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AQ24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AR24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AS24" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AT24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AU24" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AV24" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AW24" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AX24" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AY24" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AZ24" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BA24" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BB24" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC24" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD24" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="BE24" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF24" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BG24" t="n">
         <v>0</v>
@@ -5284,7 +5284,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Bulgaria First League</t>
+          <t>Serbia SuperLiga</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -5294,12 +5294,12 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Slavia Sofia</t>
+          <t>Spartak Subotica</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Botev Plovdiv</t>
+          <t>Radnik Surdulica</t>
         </is>
       </c>
       <c r="G25" t="n">
@@ -5332,79 +5332,79 @@
         </is>
       </c>
       <c r="P25" t="n">
-        <v>2.83</v>
+        <v>2.88</v>
       </c>
       <c r="Q25" t="n">
-        <v>3.24</v>
+        <v>3.1</v>
       </c>
       <c r="R25" t="n">
-        <v>2.43</v>
+        <v>2.4</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AE25" t="n">
-        <v>1.84</v>
+        <v>2.19</v>
       </c>
       <c r="AF25" t="n">
-        <v>1.84</v>
+        <v>1.6</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>3.98</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AO25" t="n">
         <v>0</v>
@@ -5446,19 +5446,19 @@
         <v>0</v>
       </c>
       <c r="BB25" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BC25" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="BD25" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE25" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF25" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="BG25" t="n">
         <v>0</v>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Russia FNL</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -5491,12 +5491,12 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Aluminij</t>
+          <t>Rotor Volgograd</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Maribor</t>
+          <t>Fakel</t>
         </is>
       </c>
       <c r="G26" t="n">
@@ -5529,79 +5529,79 @@
         </is>
       </c>
       <c r="P26" t="n">
-        <v>4.66</v>
+        <v>2.98</v>
       </c>
       <c r="Q26" t="n">
-        <v>4.1</v>
+        <v>2.67</v>
       </c>
       <c r="R26" t="n">
+        <v>2.79</v>
+      </c>
+      <c r="S26" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2.98</v>
+      </c>
+      <c r="V26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="W26" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="X26" t="n">
+        <v>3.88</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="AA26" t="n">
+        <v>1.04</v>
+      </c>
+      <c r="AB26" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="AC26" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AD26" t="n">
+        <v>2.36</v>
+      </c>
+      <c r="AE26" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AF26" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="AG26" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH26" t="n">
+        <v>1.08</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AL26" t="n">
         <v>1.56</v>
       </c>
-      <c r="S26" t="n">
-        <v>0</v>
-      </c>
-      <c r="T26" t="n">
-        <v>0</v>
-      </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL26" t="n">
-        <v>0</v>
-      </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AO26" t="n">
         <v>0</v>
@@ -5643,19 +5643,19 @@
         <v>0</v>
       </c>
       <c r="BB26" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="BC26" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="BD26" t="n">
-        <v>0</v>
+        <v>2.81</v>
       </c>
       <c r="BE26" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BF26" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="BG26" t="n">
         <v>0</v>
@@ -5678,7 +5678,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Russia FNL</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -5688,12 +5688,12 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Rotor Volgograd</t>
+          <t>Aluminij</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Fakel</t>
+          <t>Maribor</t>
         </is>
       </c>
       <c r="G27" t="n">
@@ -5726,79 +5726,79 @@
         </is>
       </c>
       <c r="P27" t="n">
-        <v>2.98</v>
+        <v>4.4</v>
       </c>
       <c r="Q27" t="n">
-        <v>2.67</v>
+        <v>3.9</v>
       </c>
       <c r="R27" t="n">
-        <v>2.79</v>
+        <v>1.57</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>4.75</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AO27" t="n">
         <v>0</v>
@@ -5840,19 +5840,19 @@
         <v>0</v>
       </c>
       <c r="BB27" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC27" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BD27" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="BE27" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BF27" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG27" t="n">
         <v>0</v>
@@ -5875,22 +5875,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Maccabi Herzliya</t>
+          <t>Ogre United</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Maccabi Kabilio Jaffa</t>
+          <t>Liepāja</t>
         </is>
       </c>
       <c r="G28" t="n">
@@ -6072,7 +6072,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -6082,12 +6082,12 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Ironi Modi'in FC</t>
+          <t>Piast Gliwice</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Hapoel Ramat Gan</t>
+          <t>Radomiak Radom</t>
         </is>
       </c>
       <c r="G29" t="n">
@@ -6120,133 +6120,133 @@
         </is>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>3.21</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>2.98</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>3.29</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>5.75</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AO29" t="n">
         <v>0</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AQ29" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AR29" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AS29" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AT29" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU29" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AV29" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW29" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX29" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AY29" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="BA29" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="BB29" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC29" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD29" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="BE29" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF29" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG29" t="n">
         <v>0</v>
@@ -6269,7 +6269,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -6279,12 +6279,12 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Kiryat Yam SC</t>
+          <t>FCSB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Maccabi Petah Tikva</t>
+          <t>UTA Arad</t>
         </is>
       </c>
       <c r="G30" t="n">
@@ -6317,133 +6317,133 @@
         </is>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>5.84</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>6.15</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AO30" t="n">
         <v>0</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="AQ30" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AR30" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AS30" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AT30" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AU30" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AV30" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AW30" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AX30" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AY30" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="BA30" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="BB30" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC30" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BD30" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="BE30" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BF30" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG30" t="n">
         <v>0</v>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -6476,12 +6476,12 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Hapoel Nazareth Illit</t>
+          <t>Admira</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bnei Yehuda</t>
+          <t>Rapid Wien II</t>
         </is>
       </c>
       <c r="G31" t="n">
@@ -6514,79 +6514,79 @@
         </is>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="Q31" t="n">
-        <v>0</v>
+        <v>5.32</v>
       </c>
       <c r="R31" t="n">
-        <v>0</v>
+        <v>8.369999999999999</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="AO31" t="n">
         <v>0</v>
@@ -6628,19 +6628,19 @@
         <v>0</v>
       </c>
       <c r="BB31" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BC31" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BD31" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE31" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BF31" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BG31" t="n">
         <v>0</v>
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -6673,12 +6673,12 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Shalem</t>
+          <t>Liefering</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Hapoel Hadera</t>
+          <t>WSPG Wels</t>
         </is>
       </c>
       <c r="G32" t="n">
@@ -6711,79 +6711,79 @@
         </is>
       </c>
       <c r="P32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>4.09</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>6.55</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>5.51</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AO32" t="n">
         <v>0</v>
@@ -6825,19 +6825,19 @@
         <v>0</v>
       </c>
       <c r="BB32" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="BC32" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD32" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE32" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="BF32" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG32" t="n">
         <v>0</v>
@@ -6860,7 +6860,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>FCSB</t>
+          <t>Austria Klagenfurt</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>UTA Arad</t>
+          <t>First Vienna</t>
         </is>
       </c>
       <c r="G33" t="n">
@@ -6908,79 +6908,79 @@
         </is>
       </c>
       <c r="P33" t="n">
-        <v>1.63</v>
+        <v>2.89</v>
       </c>
       <c r="Q33" t="n">
-        <v>3.55</v>
+        <v>3.2</v>
       </c>
       <c r="R33" t="n">
-        <v>5.55</v>
+        <v>2.2</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>3.81</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>6.95</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AO33" t="n">
         <v>0</v>
@@ -7022,19 +7022,19 @@
         <v>0</v>
       </c>
       <c r="BB33" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="BC33" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="BD33" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="BE33" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="BF33" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BG33" t="n">
         <v>0</v>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Hapoel Rishon LeZion</t>
+          <t>St. Pölten</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Hapoel Acre</t>
+          <t>Austria Salzburg</t>
         </is>
       </c>
       <c r="G34" t="n">
@@ -7105,13 +7105,13 @@
         </is>
       </c>
       <c r="P34" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Q34" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="R34" t="n">
-        <v>0</v>
+        <v>4.95</v>
       </c>
       <c r="S34" t="n">
         <v>0</v>
@@ -7150,10 +7150,10 @@
         <v>0</v>
       </c>
       <c r="AE34" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF34" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG34" t="n">
         <v>0</v>
@@ -7254,7 +7254,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Croatia Prva HNL</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -7264,12 +7264,12 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Piast Gliwice</t>
+          <t>Istra 1961</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Radomiak Radom</t>
+          <t>Varaždin</t>
         </is>
       </c>
       <c r="G35" t="n">
@@ -7302,133 +7302,133 @@
         </is>
       </c>
       <c r="P35" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="Q35" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="R35" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="S35" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="T35" t="n">
+        <v>1.99</v>
+      </c>
+      <c r="U35" t="n">
+        <v>3.36</v>
+      </c>
+      <c r="V35" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="W35" t="n">
+        <v>2.39</v>
+      </c>
+      <c r="X35" t="n">
+        <v>2.95</v>
+      </c>
+      <c r="Y35" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="Z35" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="AA35" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AB35" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="AC35" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD35" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE35" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="AF35" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AG35" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AH35" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI35" t="n">
+        <v>6.6</v>
+      </c>
+      <c r="AJ35" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AK35" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AL35" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM35" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1.43</v>
+      </c>
+      <c r="AO35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY35" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA35" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB35" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="BC35" t="n">
         <v>2.2</v>
       </c>
-      <c r="Q35" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="R35" t="n">
-        <v>3.17</v>
-      </c>
-      <c r="S35" t="n">
-        <v>0</v>
-      </c>
-      <c r="T35" t="n">
-        <v>0</v>
-      </c>
-      <c r="U35" t="n">
-        <v>0</v>
-      </c>
-      <c r="V35" t="n">
-        <v>0</v>
-      </c>
-      <c r="W35" t="n">
-        <v>0</v>
-      </c>
-      <c r="X35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY35" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB35" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC35" t="n">
-        <v>0</v>
-      </c>
       <c r="BD35" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="BE35" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BF35" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BG35" t="n">
         <v>0</v>
@@ -7451,22 +7451,22 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Ogre United</t>
+          <t>České Budějovice</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Liepāja</t>
+          <t>Viktoria Žižkov</t>
         </is>
       </c>
       <c r="G36" t="n">
@@ -7648,7 +7648,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -7658,12 +7658,12 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Znicz Pruszków</t>
+          <t>Kiryat Yam SC</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stal Rzeszów</t>
+          <t>Maccabi Petah Tikva</t>
         </is>
       </c>
       <c r="G37" t="n">
@@ -7696,13 +7696,13 @@
         </is>
       </c>
       <c r="P37" t="n">
-        <v>2.22</v>
+        <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="R37" t="n">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="S37" t="n">
         <v>0</v>
@@ -7845,7 +7845,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Sparta Praha II</t>
+          <t>Ironi Modi'in FC</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Vlašim</t>
+          <t>Hapoel Ramat Gan</t>
         </is>
       </c>
       <c r="G38" t="n">
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -8052,12 +8052,12 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Austria Klagenfurt</t>
+          <t>Znicz Pruszków</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>First Vienna</t>
+          <t>Stal Rzeszów</t>
         </is>
       </c>
       <c r="G39" t="n">
@@ -8090,13 +8090,13 @@
         </is>
       </c>
       <c r="P39" t="n">
-        <v>2.81</v>
+        <v>2.22</v>
       </c>
       <c r="Q39" t="n">
-        <v>3.46</v>
+        <v>3.5</v>
       </c>
       <c r="R39" t="n">
-        <v>2.32</v>
+        <v>2.92</v>
       </c>
       <c r="S39" t="n">
         <v>0</v>
@@ -8135,10 +8135,10 @@
         <v>0</v>
       </c>
       <c r="AE39" t="n">
-        <v>1.99</v>
+        <v>0</v>
       </c>
       <c r="AF39" t="n">
-        <v>1.78</v>
+        <v>0</v>
       </c>
       <c r="AG39" t="n">
         <v>0</v>
@@ -8239,7 +8239,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Czech Republic FNL</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -8249,12 +8249,12 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Hapoel Kfar Saba</t>
+          <t>Sparta Praha II</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kafr Qasim</t>
+          <t>Vlašim</t>
         </is>
       </c>
       <c r="G40" t="n">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Czech Republic FNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -8446,12 +8446,12 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Příbram</t>
+          <t>Hapoel Rishon LeZion</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Slavia Praha U21</t>
+          <t>Hapoel Acre</t>
         </is>
       </c>
       <c r="G41" t="n">
@@ -8633,7 +8633,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -8643,12 +8643,12 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Liefering</t>
+          <t>Hapoel Kfar Saba</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>WSPG Wels</t>
+          <t>Kafr Qasim</t>
         </is>
       </c>
       <c r="G42" t="n">
@@ -8681,13 +8681,13 @@
         </is>
       </c>
       <c r="P42" t="n">
-        <v>1.77</v>
+        <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="R42" t="n">
-        <v>4.09</v>
+        <v>0</v>
       </c>
       <c r="S42" t="n">
         <v>0</v>
@@ -8726,10 +8726,10 @@
         <v>0</v>
       </c>
       <c r="AE42" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AF42" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="AG42" t="n">
         <v>0</v>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -8840,12 +8840,12 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Admira</t>
+          <t>Maccabi Herzliya</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rapid Wien II</t>
+          <t>Maccabi Kabilio Jaffa</t>
         </is>
       </c>
       <c r="G43" t="n">
@@ -8878,13 +8878,13 @@
         </is>
       </c>
       <c r="P43" t="n">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>5.32</v>
+        <v>0</v>
       </c>
       <c r="R43" t="n">
-        <v>8.369999999999999</v>
+        <v>0</v>
       </c>
       <c r="S43" t="n">
         <v>0</v>
@@ -9027,7 +9027,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -9037,12 +9037,12 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>St. Pölten</t>
+          <t>Hapoel Nazareth Illit</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Austria Salzburg</t>
+          <t>Bnei Yehuda</t>
         </is>
       </c>
       <c r="G44" t="n">
@@ -9075,13 +9075,13 @@
         </is>
       </c>
       <c r="P44" t="n">
-        <v>1.54</v>
+        <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4.2</v>
+        <v>0</v>
       </c>
       <c r="R44" t="n">
-        <v>5.37</v>
+        <v>0</v>
       </c>
       <c r="S44" t="n">
         <v>0</v>
@@ -9120,10 +9120,10 @@
         <v>0</v>
       </c>
       <c r="AE44" t="n">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="AF44" t="n">
-        <v>1.84</v>
+        <v>0</v>
       </c>
       <c r="AG44" t="n">
         <v>0</v>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Croatia Prva HNL</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Istra 1961</t>
+          <t>Hapoel Ra'anana</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Varaždin</t>
+          <t>Hapoel Afula</t>
         </is>
       </c>
       <c r="G45" t="n">
@@ -9421,22 +9421,22 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Norway Toppserien</t>
+          <t>Israel Liga Leumit</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Bodø / Glimt W</t>
+          <t>Hapoel Kfar Shalem</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Hønefoss Women</t>
+          <t>Hapoel Hadera</t>
         </is>
       </c>
       <c r="G46" t="n">
@@ -9628,12 +9628,12 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Molde W</t>
+          <t>Bodø / Glimt W</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Brann W</t>
+          <t>Hønefoss Women</t>
         </is>
       </c>
       <c r="G47" t="n">
@@ -9825,12 +9825,12 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>České Budějovice</t>
+          <t>Příbram</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Viktoria Žižkov</t>
+          <t>Slavia Praha U21</t>
         </is>
       </c>
       <c r="G48" t="n">
@@ -10012,22 +10012,22 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Israel Liga Leumit</t>
+          <t>Norway Toppserien</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Hapoel Ra'anana</t>
+          <t>Molde W</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Hapoel Afula</t>
+          <t>Brann W</t>
         </is>
       </c>
       <c r="G49" t="n">
@@ -10266,13 +10266,13 @@
         <v>2.22</v>
       </c>
       <c r="S50" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="T50" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U50" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V50" t="n">
         <v>0</v>
@@ -10281,10 +10281,10 @@
         <v>0</v>
       </c>
       <c r="X50" t="n">
-        <v>0</v>
+        <v>2.32</v>
       </c>
       <c r="Y50" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="Z50" t="n">
         <v>0</v>
@@ -10296,40 +10296,40 @@
         <v>0</v>
       </c>
       <c r="AC50" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AD50" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="AE50" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF50" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG50" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="AH50" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI50" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AJ50" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AK50" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL50" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AM50" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN50" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AO50" t="n">
         <v>0</v>
@@ -10374,13 +10374,13 @@
         <v>0</v>
       </c>
       <c r="BC50" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="BD50" t="n">
         <v>0</v>
       </c>
       <c r="BE50" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="BF50" t="n">
         <v>0</v>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Germany 2. Bundesliga</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -10416,12 +10416,12 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Cagliari</t>
+          <t>Karlsruher SC</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Napoli</t>
+          <t>Greuther Fürth</t>
         </is>
       </c>
       <c r="G51" t="n">
@@ -10454,13 +10454,13 @@
         </is>
       </c>
       <c r="P51" t="n">
-        <v>5.88</v>
+        <v>2.01</v>
       </c>
       <c r="Q51" t="n">
         <v>3.75</v>
       </c>
       <c r="R51" t="n">
-        <v>1.73</v>
+        <v>3.26</v>
       </c>
       <c r="S51" t="n">
         <v>0</v>
@@ -10800,7 +10800,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Germany 2. Bundesliga</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -10810,12 +10810,12 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Karlsruher SC</t>
+          <t>Cagliari</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Greuther Fürth</t>
+          <t>Napoli</t>
         </is>
       </c>
       <c r="G53" t="n">
@@ -10848,133 +10848,133 @@
         </is>
       </c>
       <c r="P53" t="n">
-        <v>2.01</v>
+        <v>5.6</v>
       </c>
       <c r="Q53" t="n">
-        <v>3.75</v>
+        <v>3.82</v>
       </c>
       <c r="R53" t="n">
-        <v>3.26</v>
+        <v>1.61</v>
       </c>
       <c r="S53" t="n">
-        <v>0</v>
+        <v>6.63</v>
       </c>
       <c r="T53" t="n">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="U53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="V53" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W53" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="X53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y53" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="Z53" t="n">
-        <v>0</v>
+        <v>8.5</v>
       </c>
       <c r="AA53" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AB53" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC53" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD53" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="AE53" t="n">
-        <v>0</v>
+        <v>2.39</v>
       </c>
       <c r="AF53" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG53" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AH53" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI53" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ53" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK53" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AL53" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM53" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AN53" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AO53" t="n">
         <v>0</v>
       </c>
       <c r="AP53" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AQ53" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AR53" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AS53" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AT53" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AU53" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AV53" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AW53" t="n">
-        <v>0</v>
+        <v>1.71</v>
       </c>
       <c r="AX53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AY53" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BA53" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="BB53" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="BC53" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BD53" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BE53" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF53" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG53" t="n">
         <v>0</v>
@@ -11194,7 +11194,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Egypt Egyptian Premier League</t>
+          <t>Denmark Superliga</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -11204,12 +11204,12 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Wadi Degla</t>
+          <t>Vejle</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>El Gounah</t>
+          <t>OB</t>
         </is>
       </c>
       <c r="G55" t="n">
@@ -11242,133 +11242,133 @@
         </is>
       </c>
       <c r="P55" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="Q55" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R55" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="S55" t="n">
-        <v>0</v>
+        <v>3.78</v>
       </c>
       <c r="T55" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="U55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="V55" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W55" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="X55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="Y55" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="Z55" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA55" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AB55" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC55" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD55" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AE55" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG55" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AH55" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AI55" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AJ55" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK55" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL55" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM55" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AN55" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AO55" t="n">
         <v>0</v>
       </c>
       <c r="AP55" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ55" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR55" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AS55" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT55" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AU55" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AV55" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW55" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AX55" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY55" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="BA55" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="BB55" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC55" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BD55" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="BE55" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="BF55" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BG55" t="n">
         <v>0</v>
@@ -11391,7 +11391,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Denmark Superliga</t>
+          <t>Germany 3. Liga</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -11401,12 +11401,12 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Vejle</t>
+          <t>Wehen Wiesbaden</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>OB</t>
+          <t>Hansa Rostock</t>
         </is>
       </c>
       <c r="G56" t="n">
@@ -11439,79 +11439,79 @@
         </is>
       </c>
       <c r="P56" t="n">
-        <v>2.99</v>
+        <v>3.25</v>
       </c>
       <c r="Q56" t="n">
-        <v>3.65</v>
+        <v>3.5</v>
       </c>
       <c r="R56" t="n">
-        <v>2.18</v>
+        <v>2</v>
       </c>
       <c r="S56" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="T56" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="U56" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V56" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="W56" t="n">
-        <v>0</v>
+        <v>3.02</v>
       </c>
       <c r="X56" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="Y56" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="Z56" t="n">
-        <v>0</v>
+        <v>6.25</v>
       </c>
       <c r="AA56" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB56" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC56" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AD56" t="n">
-        <v>0</v>
+        <v>3.96</v>
       </c>
       <c r="AE56" t="n">
-        <v>0</v>
+        <v>1.72</v>
       </c>
       <c r="AF56" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG56" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="AH56" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AI56" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AJ56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AK56" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL56" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AM56" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AN56" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AO56" t="n">
         <v>0</v>
@@ -11553,19 +11553,19 @@
         <v>0</v>
       </c>
       <c r="BB56" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="BC56" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="BD56" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BE56" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="BF56" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG56" t="n">
         <v>0</v>
@@ -11588,7 +11588,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Germany 3. Liga</t>
+          <t>Egypt Egyptian Premier League</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -11598,12 +11598,12 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Wehen Wiesbaden</t>
+          <t>Wadi Degla</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Hansa Rostock</t>
+          <t>El Gounah</t>
         </is>
       </c>
       <c r="G57" t="n">
@@ -11636,133 +11636,133 @@
         </is>
       </c>
       <c r="P57" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Q57" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="R57" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="S57" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T57" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="U57" t="n">
-        <v>0</v>
+        <v>4.82</v>
       </c>
       <c r="V57" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="W57" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="X57" t="n">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="Y57" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="Z57" t="n">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AA57" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB57" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC57" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AD57" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AE57" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AF57" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="AG57" t="n">
-        <v>0</v>
+        <v>5.05</v>
       </c>
       <c r="AH57" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="AI57" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AJ57" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK57" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AL57" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AM57" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AN57" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO57" t="n">
         <v>0</v>
       </c>
       <c r="AP57" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="AQ57" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AR57" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AS57" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AT57" t="n">
         <v>0</v>
       </c>
       <c r="AU57" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AV57" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AW57" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AX57" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AY57" t="n">
         <v>0</v>
       </c>
       <c r="AZ57" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="BA57" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BB57" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="BC57" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="BD57" t="n">
-        <v>0</v>
+        <v>2.78</v>
       </c>
       <c r="BE57" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="BF57" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="BG57" t="n">
         <v>0</v>
@@ -11785,7 +11785,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Austria Bundesliga</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -11795,12 +11795,12 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Concarneau</t>
+          <t>Sturm Graz</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Valenciennes</t>
+          <t>Salzburg</t>
         </is>
       </c>
       <c r="G58" t="n">
@@ -11833,13 +11833,13 @@
         </is>
       </c>
       <c r="P58" t="n">
-        <v>2.28</v>
+        <v>3.32</v>
       </c>
       <c r="Q58" t="n">
-        <v>2.75</v>
+        <v>3.66</v>
       </c>
       <c r="R58" t="n">
-        <v>3.46</v>
+        <v>2.05</v>
       </c>
       <c r="S58" t="n">
         <v>0</v>
@@ -11982,7 +11982,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Switzerland Challenge League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -11992,12 +11992,12 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Stade Nyonnais</t>
+          <t>Ajaccio</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rapperswil-Jona</t>
+          <t>Châteauroux</t>
         </is>
       </c>
       <c r="G59" t="n">
@@ -12026,17 +12026,17 @@
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P59" t="n">
-        <v>2.45</v>
+        <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="R59" t="n">
-        <v>2.75</v>
+        <v>0</v>
       </c>
       <c r="S59" t="n">
         <v>0</v>
@@ -12075,10 +12075,10 @@
         <v>0</v>
       </c>
       <c r="AE59" t="n">
-        <v>1.75</v>
+        <v>0</v>
       </c>
       <c r="AF59" t="n">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="AG59" t="n">
         <v>0</v>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Austria Bundesliga</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -12189,12 +12189,12 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Sturm Graz</t>
+          <t>Villefranche</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Salzburg</t>
+          <t>Le Puy F.43 Auvergne</t>
         </is>
       </c>
       <c r="G60" t="n">
@@ -12227,133 +12227,133 @@
         </is>
       </c>
       <c r="P60" t="n">
+        <v>3.56</v>
+      </c>
+      <c r="Q60" t="n">
+        <v>3</v>
+      </c>
+      <c r="R60" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="S60" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="V60" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="W60" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="X60" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="Y60" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="Z60" t="n">
+        <v>8.9</v>
+      </c>
+      <c r="AA60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AB60" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="AC60" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AD60" t="n">
+        <v>2.74</v>
+      </c>
+      <c r="AE60" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AF60" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="AG60" t="n">
+        <v>3.98</v>
+      </c>
+      <c r="AH60" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="AI60" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="AJ60" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="AK60" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AL60" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM60" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AO60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY60" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA60" t="n">
+        <v>0</v>
+      </c>
+      <c r="BB60" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="BC60" t="n">
+        <v>2.33</v>
+      </c>
+      <c r="BD60" t="n">
         <v>3.32</v>
       </c>
-      <c r="Q60" t="n">
-        <v>3.66</v>
-      </c>
-      <c r="R60" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="S60" t="n">
-        <v>0</v>
-      </c>
-      <c r="T60" t="n">
-        <v>0</v>
-      </c>
-      <c r="U60" t="n">
-        <v>0</v>
-      </c>
-      <c r="V60" t="n">
-        <v>0</v>
-      </c>
-      <c r="W60" t="n">
-        <v>0</v>
-      </c>
-      <c r="X60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y60" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AL60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AM60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AP60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AQ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AR60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AS60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AT60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AV60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AX60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY60" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BB60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BC60" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD60" t="n">
-        <v>0</v>
-      </c>
       <c r="BE60" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF60" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="BG60" t="n">
         <v>0</v>
@@ -12386,12 +12386,12 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Versailles</t>
+          <t>Concarneau</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Fleury 91</t>
+          <t>Valenciennes</t>
         </is>
       </c>
       <c r="G61" t="n">
@@ -12424,79 +12424,79 @@
         </is>
       </c>
       <c r="P61" t="n">
-        <v>2.14</v>
+        <v>2.28</v>
       </c>
       <c r="Q61" t="n">
-        <v>3.1</v>
+        <v>2.75</v>
       </c>
       <c r="R61" t="n">
-        <v>3.35</v>
+        <v>3.46</v>
       </c>
       <c r="S61" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="T61" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U61" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="V61" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W61" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="X61" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y61" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="Z61" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="AA61" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AB61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC61" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AD61" t="n">
-        <v>0</v>
+        <v>3.11</v>
       </c>
       <c r="AE61" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AF61" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG61" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="AH61" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="AI61" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AJ61" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AK61" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AL61" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AM61" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN61" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AO61" t="n">
         <v>0</v>
@@ -12538,19 +12538,19 @@
         <v>0</v>
       </c>
       <c r="BB61" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="BC61" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD61" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="BE61" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF61" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="BG61" t="n">
         <v>0</v>
@@ -12583,12 +12583,12 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Paris 13 Atletico</t>
+          <t>Aubagne</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Rouen</t>
+          <t>Sochaux</t>
         </is>
       </c>
       <c r="G62" t="n">
@@ -12621,79 +12621,79 @@
         </is>
       </c>
       <c r="P62" t="n">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="Q62" t="n">
-        <v>3</v>
+        <v>3.2</v>
       </c>
       <c r="R62" t="n">
         <v>2.02</v>
       </c>
       <c r="S62" t="n">
-        <v>0</v>
+        <v>4.19</v>
       </c>
       <c r="T62" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U62" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="V62" t="n">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="W62" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="X62" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="Y62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z62" t="n">
-        <v>0</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="AA62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AB62" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC62" t="n">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AD62" t="n">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="AE62" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="AF62" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AG62" t="n">
-        <v>0</v>
+        <v>3.74</v>
       </c>
       <c r="AH62" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AI62" t="n">
-        <v>0</v>
+        <v>7.7</v>
       </c>
       <c r="AJ62" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AK62" t="n">
-        <v>0</v>
+        <v>1.84</v>
       </c>
       <c r="AL62" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AM62" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AN62" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AO62" t="n">
         <v>0</v>
@@ -12735,19 +12735,19 @@
         <v>0</v>
       </c>
       <c r="BB62" t="n">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="BC62" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="BD62" t="n">
-        <v>0</v>
+        <v>3.42</v>
       </c>
       <c r="BE62" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BF62" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG62" t="n">
         <v>0</v>
@@ -12770,7 +12770,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Switzerland Challenge League</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -12780,12 +12780,12 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Aubagne</t>
+          <t>Bellinzona</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Sochaux</t>
+          <t>Stade Lausanne-Ouchy</t>
         </is>
       </c>
       <c r="G63" t="n">
@@ -12818,79 +12818,79 @@
         </is>
       </c>
       <c r="P63" t="n">
-        <v>3.55</v>
+        <v>3.85</v>
       </c>
       <c r="Q63" t="n">
-        <v>3.2</v>
+        <v>3.75</v>
       </c>
       <c r="R63" t="n">
-        <v>2.02</v>
+        <v>1.81</v>
       </c>
       <c r="S63" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="T63" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="V63" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="W63" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="X63" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="Y63" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="Z63" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AA63" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="AB63" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC63" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD63" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="AE63" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF63" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AG63" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AH63" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI63" t="n">
-        <v>0</v>
+        <v>4.55</v>
       </c>
       <c r="AJ63" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AK63" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AL63" t="n">
-        <v>0</v>
+        <v>2.19</v>
       </c>
       <c r="AM63" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AN63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO63" t="n">
         <v>0</v>
@@ -12932,19 +12932,19 @@
         <v>0</v>
       </c>
       <c r="BB63" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC63" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="BD63" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="BE63" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF63" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BG63" t="n">
         <v>0</v>
@@ -12967,22 +12967,22 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>France National</t>
+          <t>Faroe Islands Faroe Islands Premier League</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Villefranche</t>
+          <t>EB - Streymur</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Le Puy F.43 Auvergne</t>
+          <t>KÍ</t>
         </is>
       </c>
       <c r="G64" t="n">
@@ -13015,13 +13015,13 @@
         </is>
       </c>
       <c r="P64" t="n">
-        <v>3.56</v>
+        <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="R64" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="S64" t="n">
         <v>0</v>
@@ -13174,12 +13174,12 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Ajaccio</t>
+          <t>Paris 13 Atletico</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Châteauroux</t>
+          <t>Rouen</t>
         </is>
       </c>
       <c r="G65" t="n">
@@ -13208,83 +13208,83 @@
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P65" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="Q65" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="R65" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="S65" t="n">
-        <v>0</v>
+        <v>4.88</v>
       </c>
       <c r="T65" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U65" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V65" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="W65" t="n">
-        <v>0</v>
+        <v>2.49</v>
       </c>
       <c r="X65" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Y65" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z65" t="n">
-        <v>0</v>
+        <v>9.5</v>
       </c>
       <c r="AA65" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AB65" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AC65" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AD65" t="n">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="AE65" t="n">
-        <v>0</v>
+        <v>2.36</v>
       </c>
       <c r="AF65" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AG65" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="AH65" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AI65" t="n">
-        <v>0</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="AJ65" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AK65" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AL65" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AM65" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AN65" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AO65" t="n">
         <v>0</v>
@@ -13326,19 +13326,19 @@
         <v>0</v>
       </c>
       <c r="BB65" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="BC65" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="BD65" t="n">
-        <v>0</v>
+        <v>3.08</v>
       </c>
       <c r="BE65" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="BF65" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="BG65" t="n">
         <v>0</v>
@@ -13371,12 +13371,12 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Bellinzona</t>
+          <t>Stade Nyonnais</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Stade Lausanne-Ouchy</t>
+          <t>Rapperswil-Jona</t>
         </is>
       </c>
       <c r="G66" t="n">
@@ -13409,79 +13409,79 @@
         </is>
       </c>
       <c r="P66" t="n">
-        <v>4</v>
+        <v>2.29</v>
       </c>
       <c r="Q66" t="n">
-        <v>3.76</v>
+        <v>3.31</v>
       </c>
       <c r="R66" t="n">
-        <v>1.77</v>
+        <v>2.8</v>
       </c>
       <c r="S66" t="n">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T66" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="U66" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="V66" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="W66" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="X66" t="n">
-        <v>0</v>
+        <v>2.57</v>
       </c>
       <c r="Y66" t="n">
-        <v>0</v>
+        <v>1.48</v>
       </c>
       <c r="Z66" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="AA66" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AB66" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="AC66" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AD66" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AE66" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AF66" t="n">
-        <v>0</v>
+        <v>1.99</v>
       </c>
       <c r="AG66" t="n">
-        <v>0</v>
+        <v>2.76</v>
       </c>
       <c r="AH66" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AI66" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="AJ66" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="AK66" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AL66" t="n">
-        <v>0</v>
+        <v>2.28</v>
       </c>
       <c r="AM66" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AN66" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO66" t="n">
         <v>0</v>
@@ -13523,19 +13523,19 @@
         <v>0</v>
       </c>
       <c r="BB66" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="BC66" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD66" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="BE66" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF66" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="BG66" t="n">
         <v>0</v>
@@ -13558,22 +13558,22 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Faroe Islands Faroe Islands Premier League</t>
+          <t>France National</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>EB - Streymur</t>
+          <t>Versailles</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>KÍ</t>
+          <t>Fleury 91</t>
         </is>
       </c>
       <c r="G67" t="n">
@@ -13606,79 +13606,79 @@
         </is>
       </c>
       <c r="P67" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="Q67" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="R67" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S67" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="T67" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="U67" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="V67" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="W67" t="n">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X67" t="n">
-        <v>0</v>
+        <v>2.91</v>
       </c>
       <c r="Y67" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="Z67" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="AA67" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AB67" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC67" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AD67" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="AE67" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AF67" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AG67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="AH67" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AI67" t="n">
-        <v>0</v>
+        <v>7.1</v>
       </c>
       <c r="AJ67" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="AK67" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AL67" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AM67" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AN67" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="AO67" t="n">
         <v>0</v>
@@ -13720,19 +13720,19 @@
         <v>0</v>
       </c>
       <c r="BB67" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="BC67" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BD67" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="BE67" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="BF67" t="n">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="BG67" t="n">
         <v>0</v>
@@ -13765,12 +13765,12 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Cambuur</t>
+          <t>Roda JC</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>AZ II</t>
+          <t>Helmond Sport</t>
         </is>
       </c>
       <c r="G68" t="n">
@@ -13803,130 +13803,130 @@
         </is>
       </c>
       <c r="P68" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Q68" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="R68" t="n">
-        <v>0</v>
+        <v>4.49</v>
       </c>
       <c r="S68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="U68" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="V68" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="W68" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="X68" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="Y68" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="Z68" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="AA68" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AB68" t="n">
         <v>0</v>
       </c>
       <c r="AC68" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="AD68" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AE68" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AF68" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AG68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AH68" t="n">
-        <v>0</v>
+        <v>1.53</v>
       </c>
       <c r="AI68" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AJ68" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AK68" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AL68" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AM68" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AN68" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AO68" t="n">
         <v>0</v>
       </c>
       <c r="AP68" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ68" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR68" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AS68" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AT68" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AU68" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AV68" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AW68" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AX68" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AY68" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="BA68" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="BB68" t="n">
         <v>0</v>
       </c>
       <c r="BC68" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BD68" t="n">
         <v>0</v>
       </c>
       <c r="BE68" t="n">
-        <v>0</v>
+        <v>1.96</v>
       </c>
       <c r="BF68" t="n">
         <v>0</v>
@@ -13952,7 +13952,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -13962,12 +13962,12 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Amiens SC</t>
+          <t>Ajax II</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Le Mans</t>
+          <t>Almere City</t>
         </is>
       </c>
       <c r="G69" t="n">
@@ -14000,13 +14000,13 @@
         </is>
       </c>
       <c r="P69" t="n">
-        <v>3.62</v>
+        <v>0</v>
       </c>
       <c r="Q69" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="R69" t="n">
-        <v>2.03</v>
+        <v>0</v>
       </c>
       <c r="S69" t="n">
         <v>0</v>
@@ -14159,12 +14159,12 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Laval</t>
+          <t>Amiens SC</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Grenoble Foot 38</t>
+          <t>Le Mans</t>
         </is>
       </c>
       <c r="G70" t="n">
@@ -14197,13 +14197,13 @@
         </is>
       </c>
       <c r="P70" t="n">
-        <v>2.34</v>
+        <v>3.62</v>
       </c>
       <c r="Q70" t="n">
-        <v>3.05</v>
+        <v>3.35</v>
       </c>
       <c r="R70" t="n">
-        <v>3.21</v>
+        <v>2.03</v>
       </c>
       <c r="S70" t="n">
         <v>0</v>
@@ -14356,12 +14356,12 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Boulogne</t>
+          <t>Laval</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Nancy</t>
+          <t>Grenoble Foot 38</t>
         </is>
       </c>
       <c r="G71" t="n">
@@ -14394,13 +14394,13 @@
         </is>
       </c>
       <c r="P71" t="n">
-        <v>2.41</v>
+        <v>2.34</v>
       </c>
       <c r="Q71" t="n">
-        <v>3.08</v>
+        <v>3.05</v>
       </c>
       <c r="R71" t="n">
-        <v>3.06</v>
+        <v>3.21</v>
       </c>
       <c r="S71" t="n">
         <v>0</v>
@@ -14543,7 +14543,7 @@
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Hungary NB I</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -14553,12 +14553,12 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>MTK</t>
+          <t>Boulogne</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Paksi SE</t>
+          <t>Nancy</t>
         </is>
       </c>
       <c r="G72" t="n">
@@ -14591,13 +14591,13 @@
         </is>
       </c>
       <c r="P72" t="n">
-        <v>2.93</v>
+        <v>2.41</v>
       </c>
       <c r="Q72" t="n">
-        <v>3.74</v>
+        <v>3.08</v>
       </c>
       <c r="R72" t="n">
-        <v>2.04</v>
+        <v>3.06</v>
       </c>
       <c r="S72" t="n">
         <v>0</v>
@@ -14750,12 +14750,12 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Rodez</t>
+          <t>Clermont</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Bastia</t>
+          <t>Red Star</t>
         </is>
       </c>
       <c r="G73" t="n">
@@ -14788,13 +14788,13 @@
         </is>
       </c>
       <c r="P73" t="n">
-        <v>2.7</v>
+        <v>2.67</v>
       </c>
       <c r="Q73" t="n">
-        <v>3.28</v>
+        <v>3.08</v>
       </c>
       <c r="R73" t="n">
-        <v>2.52</v>
+        <v>2.69</v>
       </c>
       <c r="S73" t="n">
         <v>0</v>
@@ -14937,7 +14937,7 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eredivisie</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -14947,12 +14947,12 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>Pau</t>
+          <t>Heracles</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Montpellier</t>
+          <t>Excelsior</t>
         </is>
       </c>
       <c r="G74" t="n">
@@ -14985,13 +14985,13 @@
         </is>
       </c>
       <c r="P74" t="n">
-        <v>2.48</v>
+        <v>2.36</v>
       </c>
       <c r="Q74" t="n">
-        <v>3.36</v>
+        <v>3.7</v>
       </c>
       <c r="R74" t="n">
-        <v>2.69</v>
+        <v>2.88</v>
       </c>
       <c r="S74" t="n">
         <v>0</v>
@@ -15030,10 +15030,10 @@
         <v>0</v>
       </c>
       <c r="AE74" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AF74" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AG74" t="n">
         <v>0</v>
@@ -15144,12 +15144,12 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>PSV II</t>
+          <t>Cambuur</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vitesse</t>
+          <t>AZ II</t>
         </is>
       </c>
       <c r="G75" t="n">
@@ -15331,7 +15331,7 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -15341,12 +15341,12 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Patro Eisden</t>
+          <t>Oss</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Beerschot-Wilrijk</t>
+          <t>Eindhoven</t>
         </is>
       </c>
       <c r="G76" t="n">
@@ -15379,130 +15379,130 @@
         </is>
       </c>
       <c r="P76" t="n">
-        <v>2.88</v>
+        <v>2.29</v>
       </c>
       <c r="Q76" t="n">
-        <v>3.34</v>
+        <v>3.7</v>
       </c>
       <c r="R76" t="n">
+        <v>2.82</v>
+      </c>
+      <c r="S76" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="T76" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="U76" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="V76" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="W76" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="X76" t="n">
         <v>2.25</v>
       </c>
-      <c r="S76" t="n">
-        <v>0</v>
-      </c>
-      <c r="T76" t="n">
-        <v>0</v>
-      </c>
-      <c r="U76" t="n">
-        <v>0</v>
-      </c>
-      <c r="V76" t="n">
-        <v>0</v>
-      </c>
-      <c r="W76" t="n">
-        <v>0</v>
-      </c>
-      <c r="X76" t="n">
-        <v>0</v>
-      </c>
       <c r="Y76" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z76" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA76" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="AB76" t="n">
         <v>0</v>
       </c>
       <c r="AC76" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AD76" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AE76" t="n">
-        <v>1.92</v>
+        <v>1.6</v>
       </c>
       <c r="AF76" t="n">
-        <v>1.76</v>
+        <v>2.23</v>
       </c>
       <c r="AG76" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AH76" t="n">
-        <v>0</v>
+        <v>1.47</v>
       </c>
       <c r="AI76" t="n">
-        <v>0</v>
+        <v>4.6</v>
       </c>
       <c r="AJ76" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AK76" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AL76" t="n">
-        <v>0</v>
+        <v>2.43</v>
       </c>
       <c r="AM76" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AN76" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AO76" t="n">
         <v>0</v>
       </c>
       <c r="AP76" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AQ76" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="AR76" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AS76" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AT76" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="AU76" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AV76" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AW76" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AX76" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="AY76" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AZ76" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="BA76" t="n">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="BB76" t="n">
         <v>0</v>
       </c>
       <c r="BC76" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="BD76" t="n">
         <v>0</v>
       </c>
       <c r="BE76" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="BF76" t="n">
         <v>0</v>
@@ -15528,7 +15528,7 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -15538,12 +15538,12 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Olympic Charleroi</t>
+          <t>Pau</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>KRC Genk II</t>
+          <t>Montpellier</t>
         </is>
       </c>
       <c r="G77" t="n">
@@ -15576,13 +15576,13 @@
         </is>
       </c>
       <c r="P77" t="n">
-        <v>2.12</v>
+        <v>2.48</v>
       </c>
       <c r="Q77" t="n">
-        <v>3.6</v>
+        <v>3.36</v>
       </c>
       <c r="R77" t="n">
-        <v>2.98</v>
+        <v>2.69</v>
       </c>
       <c r="S77" t="n">
         <v>0</v>
@@ -15621,10 +15621,10 @@
         <v>0</v>
       </c>
       <c r="AE77" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AF77" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG77" t="n">
         <v>0</v>
@@ -15725,7 +15725,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Belgium First Division B</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -15735,12 +15735,12 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AS Eupen</t>
+          <t>Emmen</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>RFC Seraing</t>
+          <t>VVV</t>
         </is>
       </c>
       <c r="G78" t="n">
@@ -15773,130 +15773,130 @@
         </is>
       </c>
       <c r="P78" t="n">
-        <v>1.88</v>
+        <v>2.09</v>
       </c>
       <c r="Q78" t="n">
-        <v>3.54</v>
+        <v>3.9</v>
       </c>
       <c r="R78" t="n">
-        <v>3.5</v>
+        <v>2.97</v>
       </c>
       <c r="S78" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="T78" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U78" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="V78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W78" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="X78" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y78" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z78" t="n">
-        <v>0</v>
+        <v>4.35</v>
       </c>
       <c r="AA78" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AB78" t="n">
         <v>0</v>
       </c>
       <c r="AC78" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="AD78" t="n">
-        <v>0</v>
+        <v>5.4</v>
       </c>
       <c r="AE78" t="n">
-        <v>1.82</v>
+        <v>1.46</v>
       </c>
       <c r="AF78" t="n">
-        <v>1.85</v>
+        <v>2.48</v>
       </c>
       <c r="AG78" t="n">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="AH78" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AI78" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AJ78" t="n">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="AK78" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AL78" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AM78" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AN78" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AO78" t="n">
         <v>0</v>
       </c>
       <c r="AP78" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AQ78" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AR78" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS78" t="n">
-        <v>0</v>
+        <v>1.91</v>
       </c>
       <c r="AT78" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU78" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AV78" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="AW78" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX78" t="n">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="AY78" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ78" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="BA78" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="BB78" t="n">
         <v>0</v>
       </c>
       <c r="BC78" t="n">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="BD78" t="n">
         <v>0</v>
       </c>
       <c r="BE78" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="BF78" t="n">
         <v>0</v>
@@ -15922,7 +15922,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Netherlands Eredivisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -15932,12 +15932,12 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Heracles</t>
+          <t>Olympic Charleroi</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Excelsior</t>
+          <t>KRC Genk II</t>
         </is>
       </c>
       <c r="G79" t="n">
@@ -15970,13 +15970,13 @@
         </is>
       </c>
       <c r="P79" t="n">
-        <v>2.36</v>
+        <v>2.12</v>
       </c>
       <c r="Q79" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="R79" t="n">
-        <v>2.88</v>
+        <v>2.98</v>
       </c>
       <c r="S79" t="n">
         <v>0</v>
@@ -16119,7 +16119,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -16129,12 +16129,12 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Oss</t>
+          <t>Patro Eisden</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Eindhoven</t>
+          <t>Beerschot-Wilrijk</t>
         </is>
       </c>
       <c r="G80" t="n">
@@ -16167,13 +16167,13 @@
         </is>
       </c>
       <c r="P80" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Q80" t="n">
-        <v>0</v>
+        <v>3.34</v>
       </c>
       <c r="R80" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="S80" t="n">
         <v>0</v>
@@ -16212,10 +16212,10 @@
         <v>0</v>
       </c>
       <c r="AE80" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AF80" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AG80" t="n">
         <v>0</v>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Belgium First Division B</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -16326,12 +16326,12 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Ajax II</t>
+          <t>AS Eupen</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Almere City</t>
+          <t>RFC Seraing</t>
         </is>
       </c>
       <c r="G81" t="n">
@@ -16364,13 +16364,13 @@
         </is>
       </c>
       <c r="P81" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Q81" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="R81" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="S81" t="n">
         <v>0</v>
@@ -16409,10 +16409,10 @@
         <v>0</v>
       </c>
       <c r="AE81" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AF81" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AG81" t="n">
         <v>0</v>
@@ -16523,12 +16523,12 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Emmen</t>
+          <t>Utrecht II</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>VVV</t>
+          <t>Dordrecht</t>
         </is>
       </c>
       <c r="G82" t="n">
@@ -16710,7 +16710,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>Hungary NB I</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -16720,12 +16720,12 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Roda JC</t>
+          <t>MTK</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Helmond Sport</t>
+          <t>Paksi SE</t>
         </is>
       </c>
       <c r="G83" t="n">
@@ -16758,133 +16758,133 @@
         </is>
       </c>
       <c r="P83" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Q83" t="n">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="R83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="S83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="T83" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U83" t="n">
-        <v>0</v>
+        <v>2.45</v>
       </c>
       <c r="V83" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="W83" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="X83" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="Y83" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="Z83" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="AA83" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="AB83" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AC83" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AD83" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AE83" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AF83" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="AG83" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AH83" t="n">
-        <v>0</v>
+        <v>1.69</v>
       </c>
       <c r="AI83" t="n">
-        <v>0</v>
+        <v>3.36</v>
       </c>
       <c r="AJ83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK83" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AL83" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AM83" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="AN83" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AO83" t="n">
         <v>0</v>
       </c>
       <c r="AP83" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AQ83" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AR83" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="AS83" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AT83" t="n">
-        <v>0</v>
+        <v>2.25</v>
       </c>
       <c r="AU83" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="AV83" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AW83" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AY83" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0</v>
+        <v>2.35</v>
       </c>
       <c r="BA83" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="BB83" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC83" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="BD83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BE83" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="BF83" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BG83" t="n">
         <v>0</v>
@@ -16907,7 +16907,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>France Ligue 2</t>
+          <t>Netherlands Eerste Divisie</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -16917,12 +16917,12 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Clermont</t>
+          <t>PSV II</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Red Star</t>
+          <t>Vitesse</t>
         </is>
       </c>
       <c r="G84" t="n">
@@ -16955,130 +16955,130 @@
         </is>
       </c>
       <c r="P84" t="n">
-        <v>2.67</v>
+        <v>2.65</v>
       </c>
       <c r="Q84" t="n">
-        <v>3.08</v>
+        <v>4</v>
       </c>
       <c r="R84" t="n">
-        <v>2.69</v>
+        <v>2.35</v>
       </c>
       <c r="S84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T84" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="U84" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="V84" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="W84" t="n">
-        <v>0</v>
+        <v>4.25</v>
       </c>
       <c r="X84" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="Y84" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="Z84" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="AA84" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="AB84" t="n">
         <v>0</v>
       </c>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD84" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE84" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AF84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AG84" t="n">
-        <v>0</v>
+        <v>1.82</v>
       </c>
       <c r="AH84" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="AI84" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AJ84" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AK84" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AL84" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="AM84" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AN84" t="n">
-        <v>0</v>
+        <v>1.41</v>
       </c>
       <c r="AO84" t="n">
         <v>0</v>
       </c>
       <c r="AP84" t="n">
-        <v>0</v>
+        <v>1.19</v>
       </c>
       <c r="AQ84" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR84" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS84" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AT84" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AU84" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV84" t="n">
-        <v>0</v>
+        <v>2.9</v>
       </c>
       <c r="AW84" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX84" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="AY84" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AZ84" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="BA84" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="BB84" t="n">
         <v>0</v>
       </c>
       <c r="BC84" t="n">
-        <v>0</v>
+        <v>1.52</v>
       </c>
       <c r="BD84" t="n">
         <v>0</v>
       </c>
       <c r="BE84" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="BF84" t="n">
         <v>0</v>
@@ -17104,7 +17104,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Netherlands Eerste Divisie</t>
+          <t>France Ligue 2</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -17114,12 +17114,12 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Utrecht II</t>
+          <t>Rodez</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dordrecht</t>
+          <t>Bastia</t>
         </is>
       </c>
       <c r="G85" t="n">
@@ -17152,13 +17152,13 @@
         </is>
       </c>
       <c r="P85" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="Q85" t="n">
-        <v>0</v>
+        <v>3.28</v>
       </c>
       <c r="R85" t="n">
-        <v>0</v>
+        <v>2.52</v>
       </c>
       <c r="S85" t="n">
         <v>0</v>
@@ -17358,70 +17358,70 @@
         <v>3.51</v>
       </c>
       <c r="S86" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="T86" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="U86" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="V86" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W86" t="n">
-        <v>0</v>
+        <v>3.12</v>
       </c>
       <c r="X86" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="Y86" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="Z86" t="n">
-        <v>0</v>
+        <v>6.1</v>
       </c>
       <c r="AA86" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB86" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AC86" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AD86" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AE86" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AF86" t="n">
-        <v>0</v>
+        <v>2.17</v>
       </c>
       <c r="AG86" t="n">
-        <v>0</v>
+        <v>2.33</v>
       </c>
       <c r="AH86" t="n">
-        <v>0</v>
+        <v>1.46</v>
       </c>
       <c r="AI86" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="AJ86" t="n">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="AK86" t="n">
-        <v>0</v>
+        <v>1.61</v>
       </c>
       <c r="AL86" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AM86" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN86" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO86" t="n">
         <v>0</v>
@@ -17463,19 +17463,19 @@
         <v>0</v>
       </c>
       <c r="BB86" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="BC86" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="BD86" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="BE86" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="BF86" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="BG86" t="n">
         <v>0</v>
@@ -17498,7 +17498,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Poland Ekstraklasa</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -17508,12 +17508,12 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Motor Lublin</t>
+          <t>Perugia</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Zagłębie Lubin</t>
+          <t>Sassari Torres</t>
         </is>
       </c>
       <c r="G87" t="n">
@@ -17546,13 +17546,13 @@
         </is>
       </c>
       <c r="P87" t="n">
-        <v>2.02</v>
+        <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3.45</v>
+        <v>0</v>
       </c>
       <c r="R87" t="n">
-        <v>3.46</v>
+        <v>0</v>
       </c>
       <c r="S87" t="n">
         <v>0</v>
@@ -17695,7 +17695,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Poland 1. Liga</t>
+          <t>Poland Ekstraklasa</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -17705,12 +17705,12 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Górnik Łęczna</t>
+          <t>Motor Lublin</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Pogoń Grod. Mazowiecki</t>
+          <t>Zagłębie Lubin</t>
         </is>
       </c>
       <c r="G88" t="n">
@@ -17743,13 +17743,13 @@
         </is>
       </c>
       <c r="P88" t="n">
-        <v>2.4</v>
+        <v>2.02</v>
       </c>
       <c r="Q88" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="R88" t="n">
-        <v>2.65</v>
+        <v>3.46</v>
       </c>
       <c r="S88" t="n">
         <v>0</v>
@@ -17902,12 +17902,12 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Ternana</t>
+          <t>Bra</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Sambenedettese</t>
+          <t>Arezzo</t>
         </is>
       </c>
       <c r="G89" t="n">
@@ -18089,7 +18089,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Poland 1. Liga</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -18099,12 +18099,12 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Bra</t>
+          <t>Górnik Łęczna</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Arezzo</t>
+          <t>Pogoń Grod. Mazowiecki</t>
         </is>
       </c>
       <c r="G90" t="n">
@@ -18137,13 +18137,13 @@
         </is>
       </c>
       <c r="P90" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="Q90" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="R90" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="S90" t="n">
         <v>0</v>
@@ -18286,7 +18286,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Italy Serie C Group B</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -18296,12 +18296,12 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Perugia</t>
+          <t>Virtus Verona</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Sassari Torres</t>
+          <t>AlbinoLeffe</t>
         </is>
       </c>
       <c r="G91" t="n">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Germany Bundesliga</t>
+          <t>Italy Serie C Group A</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -18493,12 +18493,12 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RB Leipzig</t>
+          <t>Trento</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Hoffenheim</t>
+          <t>Triestina</t>
         </is>
       </c>
       <c r="G92" t="n">
@@ -18531,13 +18531,13 @@
         </is>
       </c>
       <c r="P92" t="n">
-        <v>1.96</v>
+        <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="R92" t="n">
-        <v>3.78</v>
+        <v>0</v>
       </c>
       <c r="S92" t="n">
         <v>0</v>
@@ -18582,10 +18582,10 @@
         <v>0</v>
       </c>
       <c r="AG92" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AI92" t="n">
         <v>0</v>
@@ -18680,7 +18680,7 @@
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Spain Segunda División</t>
+          <t>Germany Bundesliga</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -18690,12 +18690,12 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>SD Huesca</t>
+          <t>RB Leipzig</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Almería</t>
+          <t>Hoffenheim</t>
         </is>
       </c>
       <c r="G93" t="n">
@@ -18728,133 +18728,133 @@
         </is>
       </c>
       <c r="P93" t="n">
-        <v>3.01</v>
+        <v>1.96</v>
       </c>
       <c r="Q93" t="n">
-        <v>3.38</v>
+        <v>4.16</v>
       </c>
       <c r="R93" t="n">
-        <v>2.42</v>
+        <v>3.78</v>
       </c>
       <c r="S93" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="T93" t="n">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U93" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="V93" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W93" t="n">
-        <v>0</v>
+        <v>4.05</v>
       </c>
       <c r="X93" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1.78</v>
       </c>
       <c r="Z93" t="n">
-        <v>0</v>
+        <v>4.33</v>
       </c>
       <c r="AA93" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AB93" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>5.8</v>
       </c>
       <c r="AE93" t="n">
-        <v>1.95</v>
+        <v>1.38</v>
       </c>
       <c r="AF93" t="n">
+        <v>2.76</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>1.98</v>
+      </c>
+      <c r="AH93" t="n">
         <v>1.73</v>
       </c>
-      <c r="AG93" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>0</v>
-      </c>
       <c r="AI93" t="n">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="AJ93" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AK93" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AL93" t="n">
-        <v>0</v>
+        <v>2.85</v>
       </c>
       <c r="AM93" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AN93" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AO93" t="n">
         <v>0</v>
       </c>
       <c r="AP93" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AQ93" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AR93" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AS93" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AT93" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="AU93" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="AV93" t="n">
-        <v>0</v>
+        <v>2.95</v>
       </c>
       <c r="AW93" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AX93" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AY93" t="n">
-        <v>0</v>
+        <v>1.49</v>
       </c>
       <c r="AZ93" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="BA93" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="BB93" t="n">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="BC93" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="BD93" t="n">
-        <v>0</v>
+        <v>5.5</v>
       </c>
       <c r="BE93" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="BF93" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="BG93" t="n">
         <v>0</v>
@@ -18877,7 +18877,7 @@
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Austria 2. Liga</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -18887,12 +18887,12 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Virtus Verona</t>
+          <t>Floridsdorfer AC</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>AlbinoLeffe</t>
+          <t>Austria Lustenau</t>
         </is>
       </c>
       <c r="G94" t="n">
@@ -18925,79 +18925,79 @@
         </is>
       </c>
       <c r="P94" t="n">
-        <v>0</v>
+        <v>2.46</v>
       </c>
       <c r="Q94" t="n">
-        <v>0</v>
+        <v>2.72</v>
       </c>
       <c r="R94" t="n">
-        <v>0</v>
+        <v>3.35</v>
       </c>
       <c r="S94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="T94" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="U94" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="V94" t="n">
-        <v>0</v>
+        <v>1.45</v>
       </c>
       <c r="W94" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>3.32</v>
       </c>
       <c r="Y94" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="Z94" t="n">
-        <v>0</v>
+        <v>8.4</v>
       </c>
       <c r="AA94" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AB94" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AC94" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AD94" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AE94" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="AF94" t="n">
-        <v>0</v>
+        <v>1.62</v>
       </c>
       <c r="AG94" t="n">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="AH94" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AI94" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AK94" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AL94" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AM94" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AN94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="AO94" t="n">
         <v>0</v>
@@ -19039,19 +19039,19 @@
         <v>0</v>
       </c>
       <c r="BB94" t="n">
-        <v>0</v>
+        <v>1.28</v>
       </c>
       <c r="BC94" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="BD94" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="BE94" t="n">
-        <v>0</v>
+        <v>1.5</v>
       </c>
       <c r="BF94" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="BG94" t="n">
         <v>0</v>
@@ -19074,7 +19074,7 @@
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Italy Serie C Group A</t>
+          <t>Spain Segunda División</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -19084,12 +19084,12 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Trento</t>
+          <t>SD Huesca</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Triestina</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="G95" t="n">
@@ -19122,13 +19122,13 @@
         </is>
       </c>
       <c r="P95" t="n">
-        <v>0</v>
+        <v>3.01</v>
       </c>
       <c r="Q95" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R95" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="S95" t="n">
         <v>0</v>
@@ -19167,10 +19167,10 @@
         <v>0</v>
       </c>
       <c r="AE95" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AF95" t="n">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="AG95" t="n">
         <v>0</v>
@@ -19271,7 +19271,7 @@
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Austria 2. Liga</t>
+          <t>Italy Serie C Group B</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -19281,12 +19281,12 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Floridsdorfer AC</t>
+          <t>Ternana</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Austria Lustenau</t>
+          <t>Sambenedettese</t>
         </is>
       </c>
       <c r="G96" t="n">
@@ -19319,13 +19319,13 @@
         </is>
       </c>
       <c r="P96" t="n">
-        <v>2.46</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
-        <v>2.72</v>
+        <v>0</v>
       </c>
       <c r="R96" t="n">
-        <v>3.35</v>
+        <v>0</v>
       </c>
       <c r="S96" t="n">
         <v>0</v>
@@ -19468,7 +19468,7 @@
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -19478,12 +19478,12 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>UCD</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="G97" t="n">
@@ -19516,13 +19516,13 @@
         </is>
       </c>
       <c r="P97" t="n">
-        <v>0</v>
+        <v>5.38</v>
       </c>
       <c r="Q97" t="n">
-        <v>0</v>
+        <v>3.52</v>
       </c>
       <c r="R97" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S97" t="n">
         <v>0</v>
@@ -19675,12 +19675,12 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Waterford</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G98" t="n">
@@ -19862,22 +19862,22 @@
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>France Ligue 1</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Lens</t>
+          <t>Waterford</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Angers SCO</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G99" t="n">
@@ -19910,13 +19910,13 @@
         </is>
       </c>
       <c r="P99" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="Q99" t="n">
-        <v>5.58</v>
+        <v>0</v>
       </c>
       <c r="R99" t="n">
-        <v>10.4</v>
+        <v>0</v>
       </c>
       <c r="S99" t="n">
         <v>0</v>
@@ -20069,12 +20069,12 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G100" t="n">
@@ -20107,13 +20107,13 @@
         </is>
       </c>
       <c r="P100" t="n">
-        <v>2.3</v>
+        <v>2.17</v>
       </c>
       <c r="Q100" t="n">
-        <v>3.49</v>
+        <v>3.17</v>
       </c>
       <c r="R100" t="n">
-        <v>2.81</v>
+        <v>3.33</v>
       </c>
       <c r="S100" t="n">
         <v>0</v>
@@ -20266,12 +20266,12 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>UCD</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G101" t="n">
@@ -20304,13 +20304,13 @@
         </is>
       </c>
       <c r="P101" t="n">
-        <v>5.38</v>
+        <v>2.1</v>
       </c>
       <c r="Q101" t="n">
-        <v>3.52</v>
+        <v>3.77</v>
       </c>
       <c r="R101" t="n">
-        <v>1.59</v>
+        <v>2.96</v>
       </c>
       <c r="S101" t="n">
         <v>0</v>
@@ -20349,10 +20349,10 @@
         <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AF101" t="n">
-        <v>0</v>
+        <v>1.97</v>
       </c>
       <c r="AG101" t="n">
         <v>0</v>
@@ -20453,22 +20453,22 @@
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>France Ligue 1</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Lens</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Angers SCO</t>
         </is>
       </c>
       <c r="G102" t="n">
@@ -20501,13 +20501,13 @@
         </is>
       </c>
       <c r="P102" t="n">
-        <v>2.17</v>
+        <v>1.35</v>
       </c>
       <c r="Q102" t="n">
-        <v>3.17</v>
+        <v>5.58</v>
       </c>
       <c r="R102" t="n">
-        <v>3.33</v>
+        <v>10.4</v>
       </c>
       <c r="S102" t="n">
         <v>0</v>
@@ -20660,12 +20660,12 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="G103" t="n">
@@ -20698,13 +20698,13 @@
         </is>
       </c>
       <c r="P103" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="Q103" t="n">
-        <v>3.77</v>
+        <v>3.49</v>
       </c>
       <c r="R103" t="n">
-        <v>2.96</v>
+        <v>2.81</v>
       </c>
       <c r="S103" t="n">
         <v>0</v>
@@ -20743,10 +20743,10 @@
         <v>0</v>
       </c>
       <c r="AE103" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AF103" t="n">
-        <v>1.97</v>
+        <v>0</v>
       </c>
       <c r="AG103" t="n">
         <v>0</v>
@@ -20847,7 +20847,7 @@
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Romania Liga I</t>
+          <t>Scotland Championship</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -20857,12 +20857,12 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>CFR Cluj</t>
+          <t>Partick Thistle</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Rapid Bucureşti</t>
+          <t>St. Johnstone</t>
         </is>
       </c>
       <c r="G104" t="n">
@@ -20895,13 +20895,13 @@
         </is>
       </c>
       <c r="P104" t="n">
-        <v>2.42</v>
+        <v>2.84</v>
       </c>
       <c r="Q104" t="n">
-        <v>3.22</v>
+        <v>3.24</v>
       </c>
       <c r="R104" t="n">
-        <v>2.87</v>
+        <v>2.28</v>
       </c>
       <c r="S104" t="n">
         <v>0</v>
@@ -20940,10 +20940,10 @@
         <v>0</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1.93</v>
       </c>
       <c r="AF104" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AG104" t="n">
         <v>0</v>
@@ -21241,7 +21241,7 @@
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Northern Ireland NIFL Premiership</t>
+          <t>Romania Liga I</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -21251,12 +21251,12 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Glenavon</t>
+          <t>CFR Cluj</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Larne</t>
+          <t>Rapid Bucureşti</t>
         </is>
       </c>
       <c r="G106" t="n">
@@ -21289,13 +21289,13 @@
         </is>
       </c>
       <c r="P106" t="n">
-        <v>6.01</v>
+        <v>2.42</v>
       </c>
       <c r="Q106" t="n">
-        <v>4.1</v>
+        <v>3.22</v>
       </c>
       <c r="R106" t="n">
-        <v>1.45</v>
+        <v>2.87</v>
       </c>
       <c r="S106" t="n">
         <v>0</v>
@@ -21438,7 +21438,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Italy Serie A</t>
+          <t>Northern Ireland NIFL Premiership</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -21448,12 +21448,12 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Genoa</t>
+          <t>Glenavon</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Udinese</t>
+          <t>Larne</t>
         </is>
       </c>
       <c r="G107" t="n">
@@ -21486,13 +21486,13 @@
         </is>
       </c>
       <c r="P107" t="n">
-        <v>2.36</v>
+        <v>6.01</v>
       </c>
       <c r="Q107" t="n">
-        <v>3.36</v>
+        <v>4.1</v>
       </c>
       <c r="R107" t="n">
-        <v>3.4</v>
+        <v>1.45</v>
       </c>
       <c r="S107" t="n">
         <v>0</v>
@@ -21635,7 +21635,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Scotland Championship</t>
+          <t>Italy Serie A</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -21645,12 +21645,12 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Partick Thistle</t>
+          <t>Genoa</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>St. Johnstone</t>
+          <t>Udinese</t>
         </is>
       </c>
       <c r="G108" t="n">
@@ -21683,13 +21683,13 @@
         </is>
       </c>
       <c r="P108" t="n">
-        <v>2.84</v>
+        <v>2.36</v>
       </c>
       <c r="Q108" t="n">
-        <v>3.24</v>
+        <v>3.36</v>
       </c>
       <c r="R108" t="n">
-        <v>2.28</v>
+        <v>3.4</v>
       </c>
       <c r="S108" t="n">
         <v>0</v>
@@ -21728,10 +21728,10 @@
         <v>0</v>
       </c>
       <c r="AE108" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AF108" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="AG108" t="n">
         <v>0</v>
@@ -21832,7 +21832,7 @@
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>England Championship</t>
+          <t>Spain La Liga</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -21842,12 +21842,12 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Preston North End</t>
+          <t>Villarreal</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Stoke City</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="G109" t="n">
@@ -21880,13 +21880,13 @@
         </is>
       </c>
       <c r="P109" t="n">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="Q109" t="n">
-        <v>3.13</v>
+        <v>0</v>
       </c>
       <c r="R109" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="S109" t="n">
         <v>0</v>
@@ -21925,10 +21925,10 @@
         <v>0</v>
       </c>
       <c r="AE109" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AF109" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AG109" t="n">
         <v>0</v>
@@ -22039,12 +22039,12 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Shamrock Rovers</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="G110" t="n">
@@ -22226,22 +22226,22 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>England Championship</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Preston North End</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Stoke City</t>
         </is>
       </c>
       <c r="G111" t="n">
@@ -22274,13 +22274,13 @@
         </is>
       </c>
       <c r="P111" t="n">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="Q111" t="n">
-        <v>0</v>
+        <v>3.13</v>
       </c>
       <c r="R111" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="S111" t="n">
         <v>0</v>
@@ -22319,10 +22319,10 @@
         <v>0</v>
       </c>
       <c r="AE111" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AF111" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AG111" t="n">
         <v>0</v>
@@ -22423,7 +22423,7 @@
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Spain La Liga</t>
+          <t>England Premier League</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -22433,12 +22433,12 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Real Sociedad</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="G112" t="n">
@@ -22471,13 +22471,13 @@
         </is>
       </c>
       <c r="P112" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="Q112" t="n">
-        <v>0</v>
+        <v>4.22</v>
       </c>
       <c r="R112" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="S112" t="n">
         <v>0</v>
@@ -22522,10 +22522,10 @@
         <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AH112" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="AI112" t="n">
         <v>0</v>
@@ -22620,22 +22620,22 @@
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>England Premier League</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Shamrock Rovers</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="G113" t="n">
@@ -22668,13 +22668,13 @@
         </is>
       </c>
       <c r="P113" t="n">
-        <v>3.38</v>
+        <v>0</v>
       </c>
       <c r="Q113" t="n">
-        <v>4.22</v>
+        <v>0</v>
       </c>
       <c r="R113" t="n">
-        <v>2.07</v>
+        <v>0</v>
       </c>
       <c r="S113" t="n">
         <v>0</v>
@@ -22719,10 +22719,10 @@
         <v>0</v>
       </c>
       <c r="AG113" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="AH113" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AI113" t="n">
         <v>0</v>
@@ -23211,22 +23211,22 @@
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Mačva Šabac</t>
+          <t>Racing Louisville</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dubočica</t>
+          <t>Washington Spirit</t>
         </is>
       </c>
       <c r="G116" t="n">
@@ -23259,13 +23259,13 @@
         </is>
       </c>
       <c r="P116" t="n">
-        <v>0</v>
+        <v>3.54</v>
       </c>
       <c r="Q116" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="R116" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="S116" t="n">
         <v>0</v>
@@ -23304,10 +23304,10 @@
         <v>0</v>
       </c>
       <c r="AE116" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AF116" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AG116" t="n">
         <v>0</v>
@@ -23408,22 +23408,22 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Orlando Pride</t>
+          <t>Kabel Novi Sad</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Denver Summit W</t>
+          <t>Loznica</t>
         </is>
       </c>
       <c r="G117" t="n">
@@ -23605,7 +23605,7 @@
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>Slovenia PrvaLiga</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -23615,12 +23615,12 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>OFK Vršac</t>
+          <t>Domžale</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Voždovac</t>
+          <t>Koper</t>
         </is>
       </c>
       <c r="G118" t="n">
@@ -23649,7 +23649,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>canceled</t>
         </is>
       </c>
       <c r="P118" t="n">
@@ -23812,12 +23812,12 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Borac Čačak</t>
+          <t>Mačva Šabac</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dinamo Jug</t>
+          <t>Dubočica</t>
         </is>
       </c>
       <c r="G119" t="n">
@@ -24009,12 +24009,12 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Jedinstvo Ub</t>
+          <t>Tekstilac Odžaci</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>FAP</t>
+          <t>Trajal Krusevac</t>
         </is>
       </c>
       <c r="G120" t="n">
@@ -24206,12 +24206,12 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Kabel Novi Sad</t>
+          <t>Zemun</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Loznica</t>
+          <t>Semendrija 1924</t>
         </is>
       </c>
       <c r="G121" t="n">
@@ -24403,12 +24403,12 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Zemun</t>
+          <t>OFK Vršac</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Semendrija 1924</t>
+          <t>Voždovac</t>
         </is>
       </c>
       <c r="G122" t="n">
@@ -24590,22 +24590,22 @@
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Serbia Prva Liga</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Tekstilac Odžaci</t>
+          <t>Orlando Pride</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Trajal Krusevac</t>
+          <t>Denver Summit W</t>
         </is>
       </c>
       <c r="G123" t="n">
@@ -24787,7 +24787,7 @@
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Slovenia PrvaLiga</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -24797,12 +24797,12 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Domžale</t>
+          <t>Grafičar</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Koper</t>
+          <t>Stepojevac Vaga</t>
         </is>
       </c>
       <c r="G124" t="n">
@@ -24831,7 +24831,7 @@
       </c>
       <c r="O124" t="inlineStr">
         <is>
-          <t>canceled</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="P124" t="n">
@@ -24994,12 +24994,12 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Grafičar</t>
+          <t>Jedinstvo Ub</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Stepojevac Vaga</t>
+          <t>FAP</t>
         </is>
       </c>
       <c r="G125" t="n">
@@ -25181,22 +25181,22 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Serbia Prva Liga</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Racing Louisville</t>
+          <t>Borac Čačak</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Washington Spirit</t>
+          <t>Dinamo Jug</t>
         </is>
       </c>
       <c r="G126" t="n">
@@ -25229,13 +25229,13 @@
         </is>
       </c>
       <c r="P126" t="n">
-        <v>3.54</v>
+        <v>0</v>
       </c>
       <c r="Q126" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="R126" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="S126" t="n">
         <v>0</v>
@@ -25274,10 +25274,10 @@
         <v>0</v>
       </c>
       <c r="AE126" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AF126" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AG126" t="n">
         <v>0</v>
@@ -25575,22 +25575,22 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Australia A-League</t>
+          <t>USA NWSL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>2025/2026</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Auckland</t>
+          <t>Portland Thorns</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Macarthur</t>
+          <t>Seattle Reign</t>
         </is>
       </c>
       <c r="G128" t="n">
@@ -25623,13 +25623,13 @@
         </is>
       </c>
       <c r="P128" t="n">
-        <v>1.6</v>
+        <v>1.94</v>
       </c>
       <c r="Q128" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="R128" t="n">
-        <v>5.38</v>
+        <v>4.58</v>
       </c>
       <c r="S128" t="n">
         <v>0</v>
@@ -25772,22 +25772,22 @@
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>USA NWSL</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>2025/2026</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Portland Thorns</t>
+          <t>Auckland</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Seattle Reign</t>
+          <t>Macarthur</t>
         </is>
       </c>
       <c r="G129" t="n">
@@ -25820,13 +25820,13 @@
         </is>
       </c>
       <c r="P129" t="n">
-        <v>1.94</v>
+        <v>1.6</v>
       </c>
       <c r="Q129" t="n">
-        <v>2.8</v>
+        <v>4.4</v>
       </c>
       <c r="R129" t="n">
-        <v>4.58</v>
+        <v>5.38</v>
       </c>
       <c r="S129" t="n">
         <v>0</v>
